--- a/output/version3/test/20-15/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>984</v>
+        <v>742</v>
       </c>
       <c r="C2" t="n">
-        <v>850</v>
+        <v>835</v>
       </c>
       <c r="D2" t="n">
-        <v>718</v>
+        <v>916</v>
       </c>
       <c r="E2" t="n">
-        <v>907</v>
+        <v>841</v>
       </c>
       <c r="F2" t="n">
-        <v>947</v>
+        <v>873</v>
       </c>
       <c r="G2" t="n">
-        <v>830</v>
+        <v>770</v>
       </c>
       <c r="H2" t="n">
-        <v>860</v>
+        <v>956</v>
       </c>
       <c r="I2" t="n">
-        <v>869</v>
+        <v>897</v>
       </c>
       <c r="J2" t="n">
-        <v>836</v>
+        <v>874</v>
       </c>
       <c r="K2" t="n">
-        <v>1007</v>
+        <v>970</v>
       </c>
       <c r="L2" t="n">
-        <v>880.8</v>
+        <v>867.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>844</v>
+      </c>
+      <c r="C3" t="n">
+        <v>894</v>
+      </c>
+      <c r="D3" t="n">
+        <v>911</v>
+      </c>
+      <c r="E3" t="n">
+        <v>925</v>
+      </c>
+      <c r="F3" t="n">
         <v>847</v>
       </c>
-      <c r="C3" t="n">
-        <v>949</v>
-      </c>
-      <c r="D3" t="n">
-        <v>782</v>
-      </c>
-      <c r="E3" t="n">
-        <v>855</v>
-      </c>
-      <c r="F3" t="n">
-        <v>822</v>
-      </c>
       <c r="G3" t="n">
-        <v>889</v>
+        <v>840</v>
       </c>
       <c r="H3" t="n">
-        <v>1015</v>
+        <v>939</v>
       </c>
       <c r="I3" t="n">
-        <v>956</v>
+        <v>866</v>
       </c>
       <c r="J3" t="n">
-        <v>869</v>
+        <v>933</v>
       </c>
       <c r="K3" t="n">
-        <v>855</v>
+        <v>1074</v>
       </c>
       <c r="L3" t="n">
-        <v>883.9</v>
+        <v>907.3</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>838</v>
+        <v>977</v>
       </c>
       <c r="C4" t="n">
-        <v>782</v>
+        <v>811</v>
       </c>
       <c r="D4" t="n">
-        <v>805</v>
+        <v>772</v>
       </c>
       <c r="E4" t="n">
-        <v>831</v>
+        <v>796</v>
       </c>
       <c r="F4" t="n">
-        <v>958</v>
+        <v>783</v>
       </c>
       <c r="G4" t="n">
-        <v>841</v>
+        <v>804</v>
       </c>
       <c r="H4" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I4" t="n">
-        <v>896</v>
+        <v>919</v>
       </c>
       <c r="J4" t="n">
-        <v>783</v>
+        <v>819</v>
       </c>
       <c r="K4" t="n">
-        <v>910</v>
+        <v>798</v>
       </c>
       <c r="L4" t="n">
-        <v>842</v>
+        <v>825.6</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>771</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="D5" t="n">
-        <v>801</v>
+        <v>854</v>
       </c>
       <c r="E5" t="n">
-        <v>853</v>
+        <v>803</v>
       </c>
       <c r="F5" t="n">
-        <v>874</v>
+        <v>819</v>
       </c>
       <c r="G5" t="n">
-        <v>993</v>
+        <v>730</v>
       </c>
       <c r="H5" t="n">
-        <v>808</v>
+        <v>854</v>
       </c>
       <c r="I5" t="n">
-        <v>778</v>
+        <v>829</v>
       </c>
       <c r="J5" t="n">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="K5" t="n">
-        <v>832</v>
+        <v>913</v>
       </c>
       <c r="L5" t="n">
-        <v>838.8</v>
+        <v>829.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>841</v>
+        <v>708</v>
       </c>
       <c r="C6" t="n">
-        <v>688</v>
+        <v>722</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>663</v>
       </c>
       <c r="E6" t="n">
-        <v>713</v>
+        <v>687</v>
       </c>
       <c r="F6" t="n">
-        <v>777</v>
+        <v>878</v>
       </c>
       <c r="G6" t="n">
-        <v>666</v>
+        <v>758</v>
       </c>
       <c r="H6" t="n">
-        <v>815</v>
+        <v>629</v>
       </c>
       <c r="I6" t="n">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="J6" t="n">
-        <v>740</v>
+        <v>818</v>
       </c>
       <c r="K6" t="n">
-        <v>701</v>
+        <v>887</v>
       </c>
       <c r="L6" t="n">
-        <v>738.7</v>
+        <v>745.9</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C7" t="n">
-        <v>873</v>
+        <v>798</v>
       </c>
       <c r="D7" t="n">
-        <v>888</v>
+        <v>810</v>
       </c>
       <c r="E7" t="n">
-        <v>951</v>
+        <v>858</v>
       </c>
       <c r="F7" t="n">
-        <v>775</v>
+        <v>896</v>
       </c>
       <c r="G7" t="n">
-        <v>940</v>
+        <v>1080</v>
       </c>
       <c r="H7" t="n">
-        <v>828</v>
+        <v>847</v>
       </c>
       <c r="I7" t="n">
-        <v>744</v>
+        <v>912</v>
       </c>
       <c r="J7" t="n">
-        <v>974</v>
+        <v>851</v>
       </c>
       <c r="K7" t="n">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="L7" t="n">
-        <v>855.5</v>
+        <v>863</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>763</v>
+        <v>794</v>
       </c>
       <c r="C8" t="n">
-        <v>837</v>
+        <v>888</v>
       </c>
       <c r="D8" t="n">
-        <v>891</v>
+        <v>820</v>
       </c>
       <c r="E8" t="n">
-        <v>805</v>
+        <v>899</v>
       </c>
       <c r="F8" t="n">
-        <v>878</v>
+        <v>801</v>
       </c>
       <c r="G8" t="n">
-        <v>771</v>
+        <v>883</v>
       </c>
       <c r="H8" t="n">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="I8" t="n">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="J8" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="K8" t="n">
-        <v>807</v>
+        <v>735</v>
       </c>
       <c r="L8" t="n">
-        <v>820.3</v>
+        <v>831.7</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>870</v>
+        <v>783</v>
       </c>
       <c r="C9" t="n">
-        <v>726</v>
+        <v>885</v>
       </c>
       <c r="D9" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E9" t="n">
-        <v>754</v>
+        <v>719</v>
       </c>
       <c r="F9" t="n">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="G9" t="n">
-        <v>864</v>
+        <v>748</v>
       </c>
       <c r="H9" t="n">
-        <v>833</v>
+        <v>773</v>
       </c>
       <c r="I9" t="n">
-        <v>753</v>
+        <v>959</v>
       </c>
       <c r="J9" t="n">
-        <v>876</v>
+        <v>801</v>
       </c>
       <c r="K9" t="n">
-        <v>855</v>
+        <v>886</v>
       </c>
       <c r="L9" t="n">
-        <v>803.7</v>
+        <v>807.1</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>772</v>
+        <v>942</v>
       </c>
       <c r="C10" t="n">
-        <v>782</v>
+        <v>865</v>
       </c>
       <c r="D10" t="n">
-        <v>911</v>
+        <v>798</v>
       </c>
       <c r="E10" t="n">
-        <v>739</v>
+        <v>889</v>
       </c>
       <c r="F10" t="n">
-        <v>869</v>
+        <v>923</v>
       </c>
       <c r="G10" t="n">
-        <v>779</v>
+        <v>799</v>
       </c>
       <c r="H10" t="n">
+        <v>768</v>
+      </c>
+      <c r="I10" t="n">
         <v>819</v>
       </c>
-      <c r="I10" t="n">
-        <v>804</v>
-      </c>
       <c r="J10" t="n">
-        <v>719</v>
+        <v>783</v>
       </c>
       <c r="K10" t="n">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="L10" t="n">
-        <v>811.2</v>
+        <v>854.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>932</v>
+        <v>738</v>
       </c>
       <c r="C11" t="n">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="D11" t="n">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="E11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>860</v>
+      </c>
+      <c r="G11" t="n">
+        <v>820</v>
+      </c>
+      <c r="H11" t="n">
+        <v>875</v>
+      </c>
+      <c r="I11" t="n">
+        <v>808</v>
+      </c>
+      <c r="J11" t="n">
         <v>864</v>
       </c>
-      <c r="F11" t="n">
-        <v>859</v>
-      </c>
-      <c r="G11" t="n">
-        <v>824</v>
-      </c>
-      <c r="H11" t="n">
-        <v>820</v>
-      </c>
-      <c r="I11" t="n">
-        <v>809</v>
-      </c>
-      <c r="J11" t="n">
-        <v>771</v>
-      </c>
       <c r="K11" t="n">
-        <v>903</v>
+        <v>883</v>
       </c>
       <c r="L11" t="n">
-        <v>841.4</v>
+        <v>860.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>929</v>
+        <v>829</v>
       </c>
       <c r="C12" t="n">
-        <v>1088</v>
+        <v>1063</v>
       </c>
       <c r="D12" t="n">
-        <v>875</v>
+        <v>795</v>
       </c>
       <c r="E12" t="n">
-        <v>1050</v>
+        <v>854</v>
       </c>
       <c r="F12" t="n">
-        <v>945</v>
+        <v>1003</v>
       </c>
       <c r="G12" t="n">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="H12" t="n">
-        <v>871</v>
+        <v>910</v>
       </c>
       <c r="I12" t="n">
-        <v>825</v>
+        <v>877</v>
       </c>
       <c r="J12" t="n">
-        <v>1049</v>
+        <v>1028</v>
       </c>
       <c r="K12" t="n">
-        <v>972</v>
+        <v>1116</v>
       </c>
       <c r="L12" t="n">
-        <v>958.8</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="C13" t="n">
-        <v>779</v>
+        <v>916</v>
       </c>
       <c r="D13" t="n">
-        <v>697</v>
+        <v>840</v>
       </c>
       <c r="E13" t="n">
-        <v>953</v>
+        <v>676</v>
       </c>
       <c r="F13" t="n">
-        <v>798</v>
+        <v>741</v>
       </c>
       <c r="G13" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H13" t="n">
-        <v>725</v>
+        <v>682</v>
       </c>
       <c r="I13" t="n">
-        <v>797</v>
+        <v>687</v>
       </c>
       <c r="J13" t="n">
-        <v>743</v>
+        <v>713</v>
       </c>
       <c r="K13" t="n">
-        <v>780</v>
+        <v>840</v>
       </c>
       <c r="L13" t="n">
-        <v>780.9</v>
+        <v>765.6</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>857</v>
+        <v>820</v>
       </c>
       <c r="C14" t="n">
-        <v>816</v>
+        <v>709</v>
       </c>
       <c r="D14" t="n">
-        <v>868</v>
+        <v>785</v>
       </c>
       <c r="E14" t="n">
-        <v>993</v>
+        <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>783</v>
+        <v>821</v>
       </c>
       <c r="G14" t="n">
-        <v>983</v>
+        <v>819</v>
       </c>
       <c r="H14" t="n">
-        <v>828</v>
+        <v>728</v>
       </c>
       <c r="I14" t="n">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="J14" t="n">
-        <v>881</v>
+        <v>852</v>
       </c>
       <c r="K14" t="n">
-        <v>827</v>
+        <v>767</v>
       </c>
       <c r="L14" t="n">
-        <v>863.1</v>
+        <v>785.1</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>917</v>
+        <v>1074</v>
       </c>
       <c r="C15" t="n">
-        <v>876</v>
+        <v>775</v>
       </c>
       <c r="D15" t="n">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="E15" t="n">
-        <v>869</v>
+        <v>925</v>
       </c>
       <c r="F15" t="n">
-        <v>923</v>
+        <v>957</v>
       </c>
       <c r="G15" t="n">
-        <v>819</v>
+        <v>907</v>
       </c>
       <c r="H15" t="n">
-        <v>957</v>
+        <v>858</v>
       </c>
       <c r="I15" t="n">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="J15" t="n">
-        <v>995</v>
+        <v>859</v>
       </c>
       <c r="K15" t="n">
-        <v>948</v>
+        <v>810</v>
       </c>
       <c r="L15" t="n">
-        <v>906</v>
+        <v>897.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>829</v>
+        <v>789</v>
       </c>
       <c r="C16" t="n">
-        <v>825</v>
+        <v>924</v>
       </c>
       <c r="D16" t="n">
-        <v>974</v>
+        <v>843</v>
       </c>
       <c r="E16" t="n">
+        <v>854</v>
+      </c>
+      <c r="F16" t="n">
+        <v>793</v>
+      </c>
+      <c r="G16" t="n">
+        <v>979</v>
+      </c>
+      <c r="H16" t="n">
         <v>865</v>
       </c>
-      <c r="F16" t="n">
-        <v>954</v>
-      </c>
-      <c r="G16" t="n">
-        <v>832</v>
-      </c>
-      <c r="H16" t="n">
-        <v>919</v>
-      </c>
       <c r="I16" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="J16" t="n">
-        <v>848</v>
+        <v>806</v>
       </c>
       <c r="K16" t="n">
-        <v>890</v>
+        <v>786</v>
       </c>
       <c r="L16" t="n">
-        <v>868.6</v>
+        <v>853.9</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>869</v>
+        <v>1048</v>
       </c>
       <c r="C17" t="n">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="D17" t="n">
-        <v>861</v>
+        <v>950</v>
       </c>
       <c r="E17" t="n">
-        <v>868</v>
+        <v>858</v>
       </c>
       <c r="F17" t="n">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="G17" t="n">
-        <v>835</v>
+        <v>780</v>
       </c>
       <c r="H17" t="n">
-        <v>1110</v>
+        <v>918</v>
       </c>
       <c r="I17" t="n">
-        <v>868</v>
+        <v>901</v>
       </c>
       <c r="J17" t="n">
-        <v>882</v>
+        <v>807</v>
       </c>
       <c r="K17" t="n">
-        <v>879</v>
+        <v>811</v>
       </c>
       <c r="L17" t="n">
-        <v>893.5</v>
+        <v>881.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>894</v>
+        <v>998</v>
       </c>
       <c r="C18" t="n">
         <v>834</v>
       </c>
       <c r="D18" t="n">
-        <v>889</v>
+        <v>826</v>
       </c>
       <c r="E18" t="n">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="F18" t="n">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="G18" t="n">
-        <v>790</v>
+        <v>824</v>
       </c>
       <c r="H18" t="n">
-        <v>817</v>
+        <v>856</v>
       </c>
       <c r="I18" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="J18" t="n">
-        <v>975</v>
+        <v>840</v>
       </c>
       <c r="K18" t="n">
-        <v>734</v>
+        <v>820</v>
       </c>
       <c r="L18" t="n">
-        <v>845.9</v>
+        <v>852</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>981</v>
+        <v>800</v>
       </c>
       <c r="C19" t="n">
-        <v>805</v>
+        <v>944</v>
       </c>
       <c r="D19" t="n">
-        <v>767</v>
+        <v>804</v>
       </c>
       <c r="E19" t="n">
-        <v>733</v>
+        <v>878</v>
       </c>
       <c r="F19" t="n">
-        <v>922</v>
+        <v>905</v>
       </c>
       <c r="G19" t="n">
-        <v>768</v>
+        <v>1002</v>
       </c>
       <c r="H19" t="n">
-        <v>798</v>
+        <v>848</v>
       </c>
       <c r="I19" t="n">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="J19" t="n">
-        <v>823</v>
+        <v>954</v>
       </c>
       <c r="K19" t="n">
-        <v>996</v>
+        <v>852</v>
       </c>
       <c r="L19" t="n">
-        <v>851.1</v>
+        <v>889.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1015</v>
+        <v>836</v>
       </c>
       <c r="C20" t="n">
-        <v>796</v>
+        <v>985</v>
       </c>
       <c r="D20" t="n">
-        <v>1044</v>
+        <v>994</v>
       </c>
       <c r="E20" t="n">
-        <v>983</v>
+        <v>936</v>
       </c>
       <c r="F20" t="n">
-        <v>926</v>
+        <v>1008</v>
       </c>
       <c r="G20" t="n">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="H20" t="n">
-        <v>1044</v>
+        <v>934</v>
       </c>
       <c r="I20" t="n">
-        <v>995</v>
+        <v>972</v>
       </c>
       <c r="J20" t="n">
-        <v>882</v>
+        <v>939</v>
       </c>
       <c r="K20" t="n">
-        <v>1046</v>
+        <v>808</v>
       </c>
       <c r="L20" t="n">
-        <v>970</v>
+        <v>941.4</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>800</v>
+        <v>934</v>
       </c>
       <c r="C21" t="n">
-        <v>882</v>
+        <v>726</v>
       </c>
       <c r="D21" t="n">
-        <v>805</v>
+        <v>856</v>
       </c>
       <c r="E21" t="n">
+        <v>877</v>
+      </c>
+      <c r="F21" t="n">
         <v>748</v>
       </c>
-      <c r="F21" t="n">
-        <v>869</v>
-      </c>
       <c r="G21" t="n">
-        <v>784</v>
+        <v>961</v>
       </c>
       <c r="H21" t="n">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="I21" t="n">
-        <v>767</v>
+        <v>822</v>
       </c>
       <c r="J21" t="n">
-        <v>921</v>
+        <v>813</v>
       </c>
       <c r="K21" t="n">
-        <v>920</v>
+        <v>896</v>
       </c>
       <c r="L21" t="n">
-        <v>846.8</v>
+        <v>853.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>829</v>
+        <v>872</v>
       </c>
       <c r="C22" t="n">
-        <v>912</v>
+        <v>841</v>
       </c>
       <c r="D22" t="n">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="E22" t="n">
-        <v>854</v>
+        <v>886</v>
       </c>
       <c r="F22" t="n">
-        <v>817</v>
+        <v>861</v>
       </c>
       <c r="G22" t="n">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="H22" t="n">
-        <v>752</v>
+        <v>845</v>
       </c>
       <c r="I22" t="n">
-        <v>774</v>
+        <v>983</v>
       </c>
       <c r="J22" t="n">
-        <v>767</v>
+        <v>865</v>
       </c>
       <c r="K22" t="n">
-        <v>856</v>
+        <v>790</v>
       </c>
       <c r="L22" t="n">
-        <v>824.1</v>
+        <v>859.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>918</v>
+        <v>891</v>
       </c>
       <c r="C23" t="n">
-        <v>947</v>
+        <v>1077</v>
       </c>
       <c r="D23" t="n">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="E23" t="n">
-        <v>1041</v>
+        <v>955</v>
       </c>
       <c r="F23" t="n">
-        <v>1034</v>
+        <v>862</v>
       </c>
       <c r="G23" t="n">
-        <v>973</v>
+        <v>1104</v>
       </c>
       <c r="H23" t="n">
-        <v>1081</v>
+        <v>1114</v>
       </c>
       <c r="I23" t="n">
-        <v>1094</v>
+        <v>1019</v>
       </c>
       <c r="J23" t="n">
-        <v>989</v>
+        <v>1068</v>
       </c>
       <c r="K23" t="n">
-        <v>1040</v>
+        <v>1092</v>
       </c>
       <c r="L23" t="n">
-        <v>1009.6</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="C24" t="n">
-        <v>827</v>
+        <v>877</v>
       </c>
       <c r="D24" t="n">
-        <v>939</v>
+        <v>996</v>
       </c>
       <c r="E24" t="n">
-        <v>767</v>
+        <v>998</v>
       </c>
       <c r="F24" t="n">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G24" t="n">
-        <v>993</v>
+        <v>809</v>
       </c>
       <c r="H24" t="n">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="I24" t="n">
-        <v>1069</v>
+        <v>1119</v>
       </c>
       <c r="J24" t="n">
-        <v>768</v>
+        <v>1075</v>
       </c>
       <c r="K24" t="n">
-        <v>955</v>
+        <v>1008</v>
       </c>
       <c r="L24" t="n">
-        <v>913</v>
+        <v>972.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1086</v>
+        <v>931</v>
       </c>
       <c r="C25" t="n">
-        <v>824</v>
+        <v>877</v>
       </c>
       <c r="D25" t="n">
-        <v>841</v>
+        <v>979</v>
       </c>
       <c r="E25" t="n">
-        <v>980</v>
+        <v>902</v>
       </c>
       <c r="F25" t="n">
-        <v>912</v>
+        <v>965</v>
       </c>
       <c r="G25" t="n">
-        <v>1008</v>
+        <v>898</v>
       </c>
       <c r="H25" t="n">
-        <v>1053</v>
+        <v>801</v>
       </c>
       <c r="I25" t="n">
-        <v>1009</v>
+        <v>829</v>
       </c>
       <c r="J25" t="n">
-        <v>1001</v>
+        <v>925</v>
       </c>
       <c r="K25" t="n">
-        <v>800</v>
+        <v>831</v>
       </c>
       <c r="L25" t="n">
-        <v>951.4</v>
+        <v>893.8</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>725</v>
+        <v>810</v>
       </c>
       <c r="C26" t="n">
-        <v>871</v>
+        <v>809</v>
       </c>
       <c r="D26" t="n">
-        <v>948</v>
+        <v>789</v>
       </c>
       <c r="E26" t="n">
-        <v>794</v>
+        <v>849</v>
       </c>
       <c r="F26" t="n">
-        <v>814</v>
+        <v>898</v>
       </c>
       <c r="G26" t="n">
-        <v>901</v>
+        <v>1008</v>
       </c>
       <c r="H26" t="n">
-        <v>740</v>
+        <v>757</v>
       </c>
       <c r="I26" t="n">
-        <v>716</v>
+        <v>765</v>
       </c>
       <c r="J26" t="n">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="K26" t="n">
-        <v>878</v>
+        <v>764</v>
       </c>
       <c r="L26" t="n">
-        <v>816.6</v>
+        <v>824.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="C27" t="n">
-        <v>1036</v>
+        <v>1011</v>
       </c>
       <c r="D27" t="n">
-        <v>908</v>
+        <v>962</v>
       </c>
       <c r="E27" t="n">
-        <v>982</v>
+        <v>796</v>
       </c>
       <c r="F27" t="n">
-        <v>833</v>
+        <v>947</v>
       </c>
       <c r="G27" t="n">
-        <v>933</v>
+        <v>906</v>
       </c>
       <c r="H27" t="n">
-        <v>984</v>
+        <v>860</v>
       </c>
       <c r="I27" t="n">
-        <v>907</v>
+        <v>1095</v>
       </c>
       <c r="J27" t="n">
-        <v>694</v>
+        <v>796</v>
       </c>
       <c r="K27" t="n">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="L27" t="n">
-        <v>912.1</v>
+        <v>918.2</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>944</v>
+        <v>978</v>
       </c>
       <c r="C28" t="n">
-        <v>911</v>
+        <v>807</v>
       </c>
       <c r="D28" t="n">
-        <v>834</v>
+        <v>871</v>
       </c>
       <c r="E28" t="n">
-        <v>881</v>
+        <v>949</v>
       </c>
       <c r="F28" t="n">
-        <v>1059</v>
+        <v>753</v>
       </c>
       <c r="G28" t="n">
-        <v>750</v>
+        <v>803</v>
       </c>
       <c r="H28" t="n">
-        <v>1013</v>
+        <v>983</v>
       </c>
       <c r="I28" t="n">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="J28" t="n">
-        <v>804</v>
+        <v>882</v>
       </c>
       <c r="K28" t="n">
-        <v>1076</v>
+        <v>898</v>
       </c>
       <c r="L28" t="n">
-        <v>909.7</v>
+        <v>876.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1045</v>
+        <v>894</v>
       </c>
       <c r="C29" t="n">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="D29" t="n">
-        <v>845</v>
+        <v>893</v>
       </c>
       <c r="E29" t="n">
+        <v>911</v>
+      </c>
+      <c r="F29" t="n">
+        <v>854</v>
+      </c>
+      <c r="G29" t="n">
         <v>899</v>
       </c>
-      <c r="F29" t="n">
-        <v>878</v>
-      </c>
-      <c r="G29" t="n">
-        <v>856</v>
-      </c>
       <c r="H29" t="n">
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="I29" t="n">
-        <v>1016</v>
+        <v>801</v>
       </c>
       <c r="J29" t="n">
-        <v>815</v>
+        <v>1061</v>
       </c>
       <c r="K29" t="n">
-        <v>823</v>
+        <v>906</v>
       </c>
       <c r="L29" t="n">
-        <v>901.1</v>
+        <v>909.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>930</v>
+        <v>871</v>
       </c>
       <c r="C30" t="n">
-        <v>1001</v>
+        <v>786</v>
       </c>
       <c r="D30" t="n">
-        <v>756</v>
+        <v>840</v>
       </c>
       <c r="E30" t="n">
-        <v>817</v>
+        <v>1016</v>
       </c>
       <c r="F30" t="n">
-        <v>929</v>
+        <v>880</v>
       </c>
       <c r="G30" t="n">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="H30" t="n">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="I30" t="n">
-        <v>967</v>
+        <v>1026</v>
       </c>
       <c r="J30" t="n">
-        <v>907</v>
+        <v>963</v>
       </c>
       <c r="K30" t="n">
-        <v>828</v>
+        <v>799</v>
       </c>
       <c r="L30" t="n">
-        <v>883.6</v>
+        <v>890.9</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>837</v>
+        <v>780</v>
       </c>
       <c r="C31" t="n">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="D31" t="n">
-        <v>843</v>
+        <v>781</v>
       </c>
       <c r="E31" t="n">
-        <v>836</v>
+        <v>1041</v>
       </c>
       <c r="F31" t="n">
-        <v>815</v>
+        <v>894</v>
       </c>
       <c r="G31" t="n">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="H31" t="n">
-        <v>863</v>
+        <v>938</v>
       </c>
       <c r="I31" t="n">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="J31" t="n">
-        <v>875</v>
+        <v>995</v>
       </c>
       <c r="K31" t="n">
-        <v>721</v>
+        <v>860</v>
       </c>
       <c r="L31" t="n">
-        <v>829.7</v>
+        <v>879.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C32" t="n">
-        <v>818</v>
+        <v>926</v>
       </c>
       <c r="D32" t="n">
-        <v>921</v>
+        <v>788</v>
       </c>
       <c r="E32" t="n">
-        <v>837</v>
+        <v>876</v>
       </c>
       <c r="F32" t="n">
-        <v>822</v>
+        <v>912</v>
       </c>
       <c r="G32" t="n">
-        <v>1008</v>
+        <v>737</v>
       </c>
       <c r="H32" t="n">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="I32" t="n">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="J32" t="n">
-        <v>985</v>
+        <v>836</v>
       </c>
       <c r="K32" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="L32" t="n">
-        <v>896.7</v>
+        <v>871.4</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>826</v>
+        <v>879</v>
       </c>
       <c r="C33" t="n">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="D33" t="n">
+        <v>874</v>
+      </c>
+      <c r="E33" t="n">
+        <v>853</v>
+      </c>
+      <c r="F33" t="n">
         <v>917</v>
       </c>
-      <c r="E33" t="n">
-        <v>921</v>
-      </c>
-      <c r="F33" t="n">
-        <v>869</v>
-      </c>
       <c r="G33" t="n">
-        <v>854</v>
+        <v>716</v>
       </c>
       <c r="H33" t="n">
-        <v>786</v>
+        <v>749</v>
       </c>
       <c r="I33" t="n">
-        <v>811</v>
+        <v>751</v>
       </c>
       <c r="J33" t="n">
-        <v>739</v>
+        <v>903</v>
       </c>
       <c r="K33" t="n">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="L33" t="n">
-        <v>847.1</v>
+        <v>827</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>820</v>
+        <v>737</v>
       </c>
       <c r="C34" t="n">
-        <v>919</v>
+        <v>773</v>
       </c>
       <c r="D34" t="n">
-        <v>859</v>
+        <v>778</v>
       </c>
       <c r="E34" t="n">
-        <v>840</v>
+        <v>935</v>
       </c>
       <c r="F34" t="n">
-        <v>743</v>
+        <v>975</v>
       </c>
       <c r="G34" t="n">
-        <v>790</v>
+        <v>718</v>
       </c>
       <c r="H34" t="n">
-        <v>884</v>
+        <v>923</v>
       </c>
       <c r="I34" t="n">
-        <v>696</v>
+        <v>804</v>
       </c>
       <c r="J34" t="n">
-        <v>799</v>
+        <v>856</v>
       </c>
       <c r="K34" t="n">
-        <v>832</v>
+        <v>874</v>
       </c>
       <c r="L34" t="n">
-        <v>818.2</v>
+        <v>837.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>741</v>
+        <v>806</v>
       </c>
       <c r="C35" t="n">
-        <v>830</v>
+        <v>698</v>
       </c>
       <c r="D35" t="n">
-        <v>835</v>
+        <v>780</v>
       </c>
       <c r="E35" t="n">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="F35" t="n">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="G35" t="n">
-        <v>936</v>
+        <v>876</v>
       </c>
       <c r="H35" t="n">
-        <v>847</v>
+        <v>788</v>
       </c>
       <c r="I35" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="J35" t="n">
-        <v>899</v>
+        <v>739</v>
       </c>
       <c r="K35" t="n">
-        <v>780</v>
+        <v>804</v>
       </c>
       <c r="L35" t="n">
-        <v>821.3</v>
+        <v>785.4</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>961</v>
+        <v>1035</v>
       </c>
       <c r="C36" t="n">
-        <v>876</v>
+        <v>934</v>
       </c>
       <c r="D36" t="n">
-        <v>981</v>
+        <v>926</v>
       </c>
       <c r="E36" t="n">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="F36" t="n">
-        <v>904</v>
+        <v>989</v>
       </c>
       <c r="G36" t="n">
-        <v>987</v>
+        <v>1031</v>
       </c>
       <c r="H36" t="n">
-        <v>872</v>
+        <v>794</v>
       </c>
       <c r="I36" t="n">
-        <v>1009</v>
+        <v>983</v>
       </c>
       <c r="J36" t="n">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="K36" t="n">
-        <v>1047</v>
+        <v>845</v>
       </c>
       <c r="L36" t="n">
-        <v>933.4</v>
+        <v>923.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>717</v>
+        <v>834</v>
       </c>
       <c r="C37" t="n">
-        <v>844</v>
+        <v>981</v>
       </c>
       <c r="D37" t="n">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="E37" t="n">
-        <v>729</v>
+        <v>838</v>
       </c>
       <c r="F37" t="n">
-        <v>823</v>
+        <v>774</v>
       </c>
       <c r="G37" t="n">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="H37" t="n">
-        <v>826</v>
+        <v>918</v>
       </c>
       <c r="I37" t="n">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="J37" t="n">
-        <v>950</v>
+        <v>674</v>
       </c>
       <c r="K37" t="n">
-        <v>773</v>
+        <v>851</v>
       </c>
       <c r="L37" t="n">
-        <v>806.5</v>
+        <v>823.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>866</v>
+        <v>943</v>
       </c>
       <c r="C38" t="n">
-        <v>828</v>
+        <v>961</v>
       </c>
       <c r="D38" t="n">
-        <v>801</v>
+        <v>756</v>
       </c>
       <c r="E38" t="n">
-        <v>756</v>
+        <v>834</v>
       </c>
       <c r="F38" t="n">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="G38" t="n">
-        <v>924</v>
+        <v>811</v>
       </c>
       <c r="H38" t="n">
-        <v>916</v>
+        <v>766</v>
       </c>
       <c r="I38" t="n">
-        <v>742</v>
+        <v>892</v>
       </c>
       <c r="J38" t="n">
-        <v>923</v>
+        <v>881</v>
       </c>
       <c r="K38" t="n">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="L38" t="n">
-        <v>841.8</v>
+        <v>851.1</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>818</v>
+        <v>763</v>
       </c>
       <c r="C39" t="n">
-        <v>685</v>
+        <v>845</v>
       </c>
       <c r="D39" t="n">
-        <v>881</v>
+        <v>831</v>
       </c>
       <c r="E39" t="n">
-        <v>902</v>
+        <v>761</v>
       </c>
       <c r="F39" t="n">
-        <v>822</v>
+        <v>711</v>
       </c>
       <c r="G39" t="n">
-        <v>776</v>
+        <v>747</v>
       </c>
       <c r="H39" t="n">
-        <v>929</v>
+        <v>1135</v>
       </c>
       <c r="I39" t="n">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J39" t="n">
-        <v>752</v>
+        <v>951</v>
       </c>
       <c r="K39" t="n">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="L39" t="n">
-        <v>833</v>
+        <v>848.6</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
+        <v>954</v>
+      </c>
+      <c r="C40" t="n">
         <v>876</v>
       </c>
-      <c r="C40" t="n">
-        <v>807</v>
-      </c>
       <c r="D40" t="n">
-        <v>823</v>
+        <v>923</v>
       </c>
       <c r="E40" t="n">
-        <v>833</v>
+        <v>742</v>
       </c>
       <c r="F40" t="n">
-        <v>863</v>
+        <v>983</v>
       </c>
       <c r="G40" t="n">
-        <v>962</v>
+        <v>849</v>
       </c>
       <c r="H40" t="n">
-        <v>764</v>
+        <v>913</v>
       </c>
       <c r="I40" t="n">
-        <v>841</v>
+        <v>759</v>
       </c>
       <c r="J40" t="n">
-        <v>978</v>
+        <v>908</v>
       </c>
       <c r="K40" t="n">
-        <v>839</v>
+        <v>746</v>
       </c>
       <c r="L40" t="n">
-        <v>858.6</v>
+        <v>865.3</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>824</v>
+        <v>1005</v>
       </c>
       <c r="C41" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D41" t="n">
-        <v>804</v>
+        <v>940</v>
       </c>
       <c r="E41" t="n">
-        <v>913</v>
+        <v>861</v>
       </c>
       <c r="F41" t="n">
-        <v>886</v>
+        <v>796</v>
       </c>
       <c r="G41" t="n">
-        <v>855</v>
+        <v>952</v>
       </c>
       <c r="H41" t="n">
-        <v>880</v>
+        <v>1054</v>
       </c>
       <c r="I41" t="n">
-        <v>767</v>
+        <v>923</v>
       </c>
       <c r="J41" t="n">
-        <v>860</v>
+        <v>806</v>
       </c>
       <c r="K41" t="n">
-        <v>797</v>
+        <v>820</v>
       </c>
       <c r="L41" t="n">
-        <v>837.2</v>
+        <v>894.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>780</v>
+        <v>727</v>
       </c>
       <c r="C42" t="n">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="D42" t="n">
-        <v>648</v>
+        <v>703</v>
       </c>
       <c r="E42" t="n">
-        <v>817</v>
+        <v>688</v>
       </c>
       <c r="F42" t="n">
-        <v>812</v>
+        <v>828</v>
       </c>
       <c r="G42" t="n">
-        <v>650</v>
+        <v>899</v>
       </c>
       <c r="H42" t="n">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="I42" t="n">
-        <v>916</v>
+        <v>725</v>
       </c>
       <c r="J42" t="n">
-        <v>779</v>
+        <v>733</v>
       </c>
       <c r="K42" t="n">
-        <v>878</v>
+        <v>731</v>
       </c>
       <c r="L42" t="n">
-        <v>762</v>
+        <v>739.8</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C43" t="n">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D43" t="n">
-        <v>717</v>
+        <v>927</v>
       </c>
       <c r="E43" t="n">
-        <v>901</v>
+        <v>695</v>
       </c>
       <c r="F43" t="n">
+        <v>908</v>
+      </c>
+      <c r="G43" t="n">
+        <v>887</v>
+      </c>
+      <c r="H43" t="n">
+        <v>825</v>
+      </c>
+      <c r="I43" t="n">
+        <v>884</v>
+      </c>
+      <c r="J43" t="n">
         <v>866</v>
       </c>
-      <c r="G43" t="n">
-        <v>921</v>
-      </c>
-      <c r="H43" t="n">
-        <v>878</v>
-      </c>
-      <c r="I43" t="n">
-        <v>711</v>
-      </c>
-      <c r="J43" t="n">
-        <v>860</v>
-      </c>
       <c r="K43" t="n">
-        <v>816</v>
+        <v>923</v>
       </c>
       <c r="L43" t="n">
-        <v>835.6</v>
+        <v>858.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="C44" t="n">
-        <v>871</v>
+        <v>839</v>
       </c>
       <c r="D44" t="n">
-        <v>841</v>
+        <v>913</v>
       </c>
       <c r="E44" t="n">
-        <v>762</v>
+        <v>847</v>
       </c>
       <c r="F44" t="n">
-        <v>863</v>
+        <v>822</v>
       </c>
       <c r="G44" t="n">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="H44" t="n">
-        <v>772</v>
+        <v>950</v>
       </c>
       <c r="I44" t="n">
-        <v>878</v>
+        <v>792</v>
       </c>
       <c r="J44" t="n">
-        <v>786</v>
+        <v>845</v>
       </c>
       <c r="K44" t="n">
-        <v>798</v>
+        <v>709</v>
       </c>
       <c r="L44" t="n">
-        <v>840.9</v>
+        <v>854</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>806</v>
+        <v>776</v>
       </c>
       <c r="C45" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D45" t="n">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="E45" t="n">
-        <v>846</v>
+        <v>964</v>
       </c>
       <c r="F45" t="n">
-        <v>796</v>
+        <v>984</v>
       </c>
       <c r="G45" t="n">
-        <v>789</v>
+        <v>909</v>
       </c>
       <c r="H45" t="n">
-        <v>959</v>
+        <v>850</v>
       </c>
       <c r="I45" t="n">
-        <v>1010</v>
+        <v>960</v>
       </c>
       <c r="J45" t="n">
-        <v>794</v>
+        <v>929</v>
       </c>
       <c r="K45" t="n">
-        <v>866</v>
+        <v>1026</v>
       </c>
       <c r="L45" t="n">
-        <v>856.8</v>
+        <v>911.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="C46" t="n">
-        <v>962</v>
+        <v>797</v>
       </c>
       <c r="D46" t="n">
-        <v>867</v>
+        <v>786</v>
       </c>
       <c r="E46" t="n">
-        <v>862</v>
+        <v>951</v>
       </c>
       <c r="F46" t="n">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="G46" t="n">
-        <v>763</v>
+        <v>837</v>
       </c>
       <c r="H46" t="n">
-        <v>791</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="n">
-        <v>763</v>
+        <v>854</v>
       </c>
       <c r="J46" t="n">
-        <v>855</v>
+        <v>921</v>
       </c>
       <c r="K46" t="n">
-        <v>1048</v>
+        <v>1002</v>
       </c>
       <c r="L46" t="n">
-        <v>874.1</v>
+        <v>900.4</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>969</v>
+        <v>883</v>
       </c>
       <c r="C47" t="n">
-        <v>977</v>
+        <v>818</v>
       </c>
       <c r="D47" t="n">
-        <v>1070</v>
+        <v>1013</v>
       </c>
       <c r="E47" t="n">
-        <v>977</v>
+        <v>1051</v>
       </c>
       <c r="F47" t="n">
-        <v>955</v>
+        <v>941</v>
       </c>
       <c r="G47" t="n">
-        <v>958</v>
+        <v>882</v>
       </c>
       <c r="H47" t="n">
-        <v>1020</v>
+        <v>940</v>
       </c>
       <c r="I47" t="n">
-        <v>839</v>
+        <v>1038</v>
       </c>
       <c r="J47" t="n">
-        <v>1081</v>
+        <v>1022</v>
       </c>
       <c r="K47" t="n">
-        <v>773</v>
+        <v>905</v>
       </c>
       <c r="L47" t="n">
-        <v>961.9</v>
+        <v>949.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>743</v>
+        <v>860</v>
       </c>
       <c r="C48" t="n">
-        <v>718</v>
+        <v>781</v>
       </c>
       <c r="D48" t="n">
-        <v>850</v>
+        <v>961</v>
       </c>
       <c r="E48" t="n">
-        <v>840</v>
+        <v>981</v>
       </c>
       <c r="F48" t="n">
-        <v>995</v>
+        <v>1113</v>
       </c>
       <c r="G48" t="n">
-        <v>828</v>
+        <v>686</v>
       </c>
       <c r="H48" t="n">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="I48" t="n">
-        <v>808</v>
+        <v>1003</v>
       </c>
       <c r="J48" t="n">
-        <v>830</v>
+        <v>898</v>
       </c>
       <c r="K48" t="n">
-        <v>862</v>
+        <v>786</v>
       </c>
       <c r="L48" t="n">
-        <v>824.8</v>
+        <v>885.9</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>947</v>
+        <v>799</v>
       </c>
       <c r="C49" t="n">
+        <v>940</v>
+      </c>
+      <c r="D49" t="n">
+        <v>868</v>
+      </c>
+      <c r="E49" t="n">
         <v>842</v>
       </c>
-      <c r="D49" t="n">
-        <v>935</v>
-      </c>
-      <c r="E49" t="n">
-        <v>849</v>
-      </c>
       <c r="F49" t="n">
-        <v>995</v>
+        <v>827</v>
       </c>
       <c r="G49" t="n">
-        <v>958</v>
+        <v>835</v>
       </c>
       <c r="H49" t="n">
-        <v>950</v>
+        <v>1013</v>
       </c>
       <c r="I49" t="n">
-        <v>1043</v>
+        <v>929</v>
       </c>
       <c r="J49" t="n">
-        <v>772</v>
+        <v>976</v>
       </c>
       <c r="K49" t="n">
-        <v>1052</v>
+        <v>926</v>
       </c>
       <c r="L49" t="n">
-        <v>934.3</v>
+        <v>895.5</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>685</v>
+        <v>891</v>
       </c>
       <c r="C50" t="n">
-        <v>898</v>
+        <v>991</v>
       </c>
       <c r="D50" t="n">
-        <v>958</v>
+        <v>816</v>
       </c>
       <c r="E50" t="n">
-        <v>954</v>
+        <v>800</v>
       </c>
       <c r="F50" t="n">
-        <v>989</v>
+        <v>800</v>
       </c>
       <c r="G50" t="n">
-        <v>835</v>
+        <v>984</v>
       </c>
       <c r="H50" t="n">
-        <v>899</v>
+        <v>861</v>
       </c>
       <c r="I50" t="n">
-        <v>796</v>
+        <v>849</v>
       </c>
       <c r="J50" t="n">
-        <v>783</v>
+        <v>883</v>
       </c>
       <c r="K50" t="n">
-        <v>886</v>
+        <v>920</v>
       </c>
       <c r="L50" t="n">
-        <v>868.3</v>
+        <v>879.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1023</v>
+        <v>803</v>
       </c>
       <c r="C51" t="n">
-        <v>1001</v>
+        <v>835</v>
       </c>
       <c r="D51" t="n">
-        <v>884</v>
+        <v>1063</v>
       </c>
       <c r="E51" t="n">
-        <v>893</v>
+        <v>941</v>
       </c>
       <c r="F51" t="n">
-        <v>904</v>
+        <v>935</v>
       </c>
       <c r="G51" t="n">
-        <v>943</v>
+        <v>844</v>
       </c>
       <c r="H51" t="n">
-        <v>1067</v>
+        <v>1046</v>
       </c>
       <c r="I51" t="n">
-        <v>897</v>
+        <v>849</v>
       </c>
       <c r="J51" t="n">
-        <v>978</v>
+        <v>919</v>
       </c>
       <c r="K51" t="n">
-        <v>947</v>
+        <v>747</v>
       </c>
       <c r="L51" t="n">
-        <v>953.7</v>
+        <v>898.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>867.76</v>
+        <v>864.2</v>
       </c>
       <c r="C52" t="n">
-        <v>855.74</v>
+        <v>858.12</v>
       </c>
       <c r="D52" t="n">
-        <v>854.24</v>
+        <v>857.08</v>
       </c>
       <c r="E52" t="n">
-        <v>861.9400000000001</v>
+        <v>867.66</v>
       </c>
       <c r="F52" t="n">
-        <v>875.88</v>
+        <v>873.98</v>
       </c>
       <c r="G52" t="n">
-        <v>866.76</v>
+        <v>862.72</v>
       </c>
       <c r="H52" t="n">
-        <v>879.72</v>
+        <v>874.4400000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>852.28</v>
+        <v>876.3</v>
       </c>
       <c r="J52" t="n">
-        <v>856.72</v>
+        <v>876.16</v>
       </c>
       <c r="K52" t="n">
-        <v>880.58</v>
+        <v>868.84</v>
       </c>
       <c r="L52" t="n">
-        <v>865.1620000000001</v>
+        <v>867.95</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.065402746200562</v>
+        <v>7.776345252990723</v>
       </c>
       <c r="C2" t="n">
-        <v>7.532364130020142</v>
+        <v>7.153318881988525</v>
       </c>
       <c r="D2" t="n">
-        <v>6.57973313331604</v>
+        <v>7.875489711761475</v>
       </c>
       <c r="E2" t="n">
-        <v>8.199084281921387</v>
+        <v>7.615204572677612</v>
       </c>
       <c r="F2" t="n">
-        <v>8.34421706199646</v>
+        <v>8.318895101547241</v>
       </c>
       <c r="G2" t="n">
-        <v>8.084899425506592</v>
+        <v>6.785891771316528</v>
       </c>
       <c r="H2" t="n">
-        <v>8.073909759521484</v>
+        <v>9.675018072128296</v>
       </c>
       <c r="I2" t="n">
-        <v>7.107387781143188</v>
+        <v>8.157301187515259</v>
       </c>
       <c r="J2" t="n">
-        <v>6.442599058151245</v>
+        <v>7.453121185302734</v>
       </c>
       <c r="K2" t="n">
-        <v>9.565863609313965</v>
+        <v>8.854016065597534</v>
       </c>
       <c r="L2" t="n">
-        <v>7.899546098709107</v>
+        <v>7.966460180282593</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.621901750564575</v>
+        <v>6.724541187286377</v>
       </c>
       <c r="C3" t="n">
-        <v>7.075202226638794</v>
+        <v>7.398247718811035</v>
       </c>
       <c r="D3" t="n">
-        <v>7.051073312759399</v>
+        <v>7.781752586364746</v>
       </c>
       <c r="E3" t="n">
-        <v>7.940771102905273</v>
+        <v>8.59369683265686</v>
       </c>
       <c r="F3" t="n">
-        <v>7.027085065841675</v>
+        <v>7.105090141296387</v>
       </c>
       <c r="G3" t="n">
-        <v>6.624106884002686</v>
+        <v>7.118981122970581</v>
       </c>
       <c r="H3" t="n">
-        <v>7.373687267303467</v>
+        <v>8.354806184768677</v>
       </c>
       <c r="I3" t="n">
-        <v>8.732250213623047</v>
+        <v>7.209277868270874</v>
       </c>
       <c r="J3" t="n">
-        <v>7.235068798065186</v>
+        <v>7.898000717163086</v>
       </c>
       <c r="K3" t="n">
-        <v>7.393663883209229</v>
+        <v>9.193045616149902</v>
       </c>
       <c r="L3" t="n">
-        <v>7.407481050491333</v>
+        <v>7.737743997573853</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.088941335678101</v>
+        <v>8.690865993499756</v>
       </c>
       <c r="C4" t="n">
-        <v>6.331355094909668</v>
+        <v>6.622169971466064</v>
       </c>
       <c r="D4" t="n">
-        <v>6.61414098739624</v>
+        <v>6.82064962387085</v>
       </c>
       <c r="E4" t="n">
-        <v>6.232680320739746</v>
+        <v>6.89697790145874</v>
       </c>
       <c r="F4" t="n">
-        <v>8.019554615020752</v>
+        <v>6.733375072479248</v>
       </c>
       <c r="G4" t="n">
-        <v>6.688926458358765</v>
+        <v>6.811679840087891</v>
       </c>
       <c r="H4" t="n">
-        <v>6.966257095336914</v>
+        <v>6.540330648422241</v>
       </c>
       <c r="I4" t="n">
-        <v>6.737339735031128</v>
+        <v>7.798681020736694</v>
       </c>
       <c r="J4" t="n">
-        <v>6.623115539550781</v>
+        <v>6.462066411972046</v>
       </c>
       <c r="K4" t="n">
-        <v>6.746297836303711</v>
+        <v>7.215684652328491</v>
       </c>
       <c r="L4" t="n">
-        <v>6.804860901832581</v>
+        <v>7.059248113632203</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6.013665199279785</v>
+        <v>6.403754234313965</v>
       </c>
       <c r="C5" t="n">
-        <v>6.777220487594604</v>
+        <v>7.006235122680664</v>
       </c>
       <c r="D5" t="n">
-        <v>6.149333238601685</v>
+        <v>6.571769714355469</v>
       </c>
       <c r="E5" t="n">
-        <v>7.047029972076416</v>
+        <v>6.169307231903076</v>
       </c>
       <c r="F5" t="n">
-        <v>6.325408697128296</v>
+        <v>6.531903505325317</v>
       </c>
       <c r="G5" t="n">
-        <v>8.459428548812866</v>
+        <v>6.650590896606445</v>
       </c>
       <c r="H5" t="n">
-        <v>7.198665618896484</v>
+        <v>6.563787698745728</v>
       </c>
       <c r="I5" t="n">
-        <v>5.614668607711792</v>
+        <v>7.285977840423584</v>
       </c>
       <c r="J5" t="n">
-        <v>6.567265748977661</v>
+        <v>5.765026092529297</v>
       </c>
       <c r="K5" t="n">
-        <v>6.300425291061401</v>
+        <v>6.448793649673462</v>
       </c>
       <c r="L5" t="n">
-        <v>6.645311141014099</v>
+        <v>6.539714598655701</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>6.281992197036743</v>
+        <v>6.077192068099976</v>
       </c>
       <c r="C6" t="n">
-        <v>5.719422578811646</v>
+        <v>5.754056215286255</v>
       </c>
       <c r="D6" t="n">
-        <v>5.935356140136719</v>
+        <v>5.435879468917847</v>
       </c>
       <c r="E6" t="n">
-        <v>5.380789041519165</v>
+        <v>5.584518432617188</v>
       </c>
       <c r="F6" t="n">
-        <v>6.304439306259155</v>
+        <v>8.620594501495361</v>
       </c>
       <c r="G6" t="n">
-        <v>5.739391326904297</v>
+        <v>6.041286706924438</v>
       </c>
       <c r="H6" t="n">
-        <v>6.342319488525391</v>
+        <v>5.52715015411377</v>
       </c>
       <c r="I6" t="n">
-        <v>5.857094287872314</v>
+        <v>5.535134553909302</v>
       </c>
       <c r="J6" t="n">
-        <v>6.089999675750732</v>
+        <v>7.811710357666016</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8640456199646</v>
+        <v>7.522554397583008</v>
       </c>
       <c r="L6" t="n">
-        <v>5.951484966278076</v>
+        <v>6.391007685661316</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.493895769119263</v>
+        <v>7.190213203430176</v>
       </c>
       <c r="C7" t="n">
-        <v>7.467456817626953</v>
+        <v>7.32782506942749</v>
       </c>
       <c r="D7" t="n">
-        <v>8.012580394744873</v>
+        <v>7.535338163375854</v>
       </c>
       <c r="E7" t="n">
-        <v>8.14077615737915</v>
+        <v>7.152313470840454</v>
       </c>
       <c r="F7" t="n">
-        <v>7.425087213516235</v>
+        <v>8.174196720123291</v>
       </c>
       <c r="G7" t="n">
-        <v>8.984079122543335</v>
+        <v>10.79903697967529</v>
       </c>
       <c r="H7" t="n">
-        <v>8.530746221542358</v>
+        <v>7.581730127334595</v>
       </c>
       <c r="I7" t="n">
-        <v>6.964738130569458</v>
+        <v>9.126304149627686</v>
       </c>
       <c r="J7" t="n">
-        <v>10.73411440849304</v>
+        <v>8.170276403427124</v>
       </c>
       <c r="K7" t="n">
-        <v>7.117951631546021</v>
+        <v>7.661508083343506</v>
       </c>
       <c r="L7" t="n">
-        <v>8.087142586708069</v>
+        <v>8.071874237060547</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.380322933197021</v>
+        <v>7.072513341903687</v>
       </c>
       <c r="C8" t="n">
-        <v>8.473476648330688</v>
+        <v>7.738827466964722</v>
       </c>
       <c r="D8" t="n">
-        <v>7.975760459899902</v>
+        <v>6.663588762283325</v>
       </c>
       <c r="E8" t="n">
-        <v>6.751439094543457</v>
+        <v>8.938813924789429</v>
       </c>
       <c r="F8" t="n">
-        <v>7.11198616027832</v>
+        <v>6.686479091644287</v>
       </c>
       <c r="G8" t="n">
-        <v>7.226194858551025</v>
+        <v>7.971243619918823</v>
       </c>
       <c r="H8" t="n">
-        <v>7.200753927230835</v>
+        <v>7.051055192947388</v>
       </c>
       <c r="I8" t="n">
-        <v>7.35285758972168</v>
+        <v>7.464354038238525</v>
       </c>
       <c r="J8" t="n">
-        <v>7.65507984161377</v>
+        <v>7.655516862869263</v>
       </c>
       <c r="K8" t="n">
-        <v>6.955821990966797</v>
+        <v>6.854109287261963</v>
       </c>
       <c r="L8" t="n">
-        <v>7.408369350433349</v>
+        <v>7.409650158882141</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9.119803667068481</v>
+        <v>7.070004224777222</v>
       </c>
       <c r="C9" t="n">
-        <v>7.365928411483765</v>
+        <v>7.029603481292725</v>
       </c>
       <c r="D9" t="n">
-        <v>7.12396240234375</v>
+        <v>6.558839321136475</v>
       </c>
       <c r="E9" t="n">
-        <v>7.045246124267578</v>
+        <v>7.085489273071289</v>
       </c>
       <c r="F9" t="n">
-        <v>7.007748126983643</v>
+        <v>6.762284278869629</v>
       </c>
       <c r="G9" t="n">
-        <v>8.730788946151733</v>
+        <v>6.734350204467773</v>
       </c>
       <c r="H9" t="n">
-        <v>8.124870538711548</v>
+        <v>7.048575878143311</v>
       </c>
       <c r="I9" t="n">
-        <v>6.768752574920654</v>
+        <v>8.689847946166992</v>
       </c>
       <c r="J9" t="n">
-        <v>7.444032430648804</v>
+        <v>6.692468881607056</v>
       </c>
       <c r="K9" t="n">
-        <v>7.847991704940796</v>
+        <v>8.30337929725647</v>
       </c>
       <c r="L9" t="n">
-        <v>7.657912492752075</v>
+        <v>7.197484278678894</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.787178754806519</v>
+        <v>9.263950109481812</v>
       </c>
       <c r="C10" t="n">
-        <v>7.317875146865845</v>
+        <v>7.869013547897339</v>
       </c>
       <c r="D10" t="n">
-        <v>7.972736358642578</v>
+        <v>6.48897647857666</v>
       </c>
       <c r="E10" t="n">
-        <v>6.348299026489258</v>
+        <v>8.411621570587158</v>
       </c>
       <c r="F10" t="n">
-        <v>8.078932046890259</v>
+        <v>6.640102386474609</v>
       </c>
       <c r="G10" t="n">
-        <v>6.616147756576538</v>
+        <v>6.474047422409058</v>
       </c>
       <c r="H10" t="n">
-        <v>6.600180625915527</v>
+        <v>6.803759098052979</v>
       </c>
       <c r="I10" t="n">
-        <v>6.307416439056396</v>
+        <v>7.091966867446899</v>
       </c>
       <c r="J10" t="n">
-        <v>5.990560293197632</v>
+        <v>6.649637460708618</v>
       </c>
       <c r="K10" t="n">
-        <v>7.415349245071411</v>
+        <v>7.714073181152344</v>
       </c>
       <c r="L10" t="n">
-        <v>6.943467569351196</v>
+        <v>7.340714812278748</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>8.624066352844238</v>
+        <v>6.596207857131958</v>
       </c>
       <c r="C11" t="n">
-        <v>7.506500482559204</v>
+        <v>6.612480640411377</v>
       </c>
       <c r="D11" t="n">
-        <v>6.853682518005371</v>
+        <v>6.983719110488892</v>
       </c>
       <c r="E11" t="n">
-        <v>6.916576147079468</v>
+        <v>9.369168281555176</v>
       </c>
       <c r="F11" t="n">
-        <v>7.554834127426147</v>
+        <v>6.533947467803955</v>
       </c>
       <c r="G11" t="n">
-        <v>7.397792100906372</v>
+        <v>6.198226451873779</v>
       </c>
       <c r="H11" t="n">
-        <v>6.873649597167969</v>
+        <v>7.420135736465454</v>
       </c>
       <c r="I11" t="n">
-        <v>6.93747353553772</v>
+        <v>6.449593305587769</v>
       </c>
       <c r="J11" t="n">
-        <v>6.590340614318848</v>
+        <v>7.415136098861694</v>
       </c>
       <c r="K11" t="n">
-        <v>7.899939775466919</v>
+        <v>6.670545816421509</v>
       </c>
       <c r="L11" t="n">
-        <v>7.315485525131225</v>
+        <v>7.024916076660157</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>9.027997493743896</v>
+        <v>7.887419462203979</v>
       </c>
       <c r="C12" t="n">
-        <v>8.530813455581665</v>
+        <v>9.777597188949585</v>
       </c>
       <c r="D12" t="n">
-        <v>7.121364593505859</v>
+        <v>6.522937059402466</v>
       </c>
       <c r="E12" t="n">
-        <v>8.77112078666687</v>
+        <v>6.918905019760132</v>
       </c>
       <c r="F12" t="n">
-        <v>9.96662974357605</v>
+        <v>9.188738107681274</v>
       </c>
       <c r="G12" t="n">
-        <v>9.35968542098999</v>
+        <v>8.493921518325806</v>
       </c>
       <c r="H12" t="n">
-        <v>7.397140264511108</v>
+        <v>7.193708896636963</v>
       </c>
       <c r="I12" t="n">
-        <v>7.455005168914795</v>
+        <v>9.128302335739136</v>
       </c>
       <c r="J12" t="n">
-        <v>10.12766194343567</v>
+        <v>9.271398305892944</v>
       </c>
       <c r="K12" t="n">
-        <v>9.426966905593872</v>
+        <v>10.72222805023193</v>
       </c>
       <c r="L12" t="n">
-        <v>8.718438577651977</v>
+        <v>8.510515594482422</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>6.265021085739136</v>
+        <v>6.180292129516602</v>
       </c>
       <c r="C13" t="n">
-        <v>6.717380285263062</v>
+        <v>8.355233430862427</v>
       </c>
       <c r="D13" t="n">
-        <v>6.063075542449951</v>
+        <v>6.348852872848511</v>
       </c>
       <c r="E13" t="n">
-        <v>8.07042670249939</v>
+        <v>6.913911819458008</v>
       </c>
       <c r="F13" t="n">
-        <v>6.832574844360352</v>
+        <v>6.237129926681519</v>
       </c>
       <c r="G13" t="n">
-        <v>6.442110538482666</v>
+        <v>6.50196361541748</v>
       </c>
       <c r="H13" t="n">
-        <v>6.63310718536377</v>
+        <v>6.274042844772339</v>
       </c>
       <c r="I13" t="n">
-        <v>6.769251346588135</v>
+        <v>6.185283660888672</v>
       </c>
       <c r="J13" t="n">
-        <v>6.652569532394409</v>
+        <v>6.017720222473145</v>
       </c>
       <c r="K13" t="n">
-        <v>6.701416015625</v>
+        <v>6.315447092056274</v>
       </c>
       <c r="L13" t="n">
-        <v>6.714693307876587</v>
+        <v>6.532987761497497</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.925343751907349</v>
+        <v>7.901408672332764</v>
       </c>
       <c r="C14" t="n">
-        <v>7.422079086303711</v>
+        <v>7.128381490707397</v>
       </c>
       <c r="D14" t="n">
-        <v>7.573202610015869</v>
+        <v>6.888009071350098</v>
       </c>
       <c r="E14" t="n">
-        <v>8.39464259147644</v>
+        <v>7.047074317932129</v>
       </c>
       <c r="F14" t="n">
-        <v>7.476477384567261</v>
+        <v>7.23808217048645</v>
       </c>
       <c r="G14" t="n">
-        <v>8.361191987991333</v>
+        <v>7.274511575698853</v>
       </c>
       <c r="H14" t="n">
-        <v>7.556752920150757</v>
+        <v>7.085491895675659</v>
       </c>
       <c r="I14" t="n">
-        <v>7.226581335067749</v>
+        <v>7.554190874099731</v>
       </c>
       <c r="J14" t="n">
-        <v>7.427049398422241</v>
+        <v>7.335462331771851</v>
       </c>
       <c r="K14" t="n">
-        <v>7.390392065048218</v>
+        <v>7.347967863082886</v>
       </c>
       <c r="L14" t="n">
-        <v>7.675371313095093</v>
+        <v>7.280058026313782</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>7.265547275543213</v>
+        <v>8.434821128845215</v>
       </c>
       <c r="C15" t="n">
-        <v>8.564178228378296</v>
+        <v>6.731362342834473</v>
       </c>
       <c r="D15" t="n">
-        <v>6.896443605422974</v>
+        <v>7.869468450546265</v>
       </c>
       <c r="E15" t="n">
-        <v>7.623578310012817</v>
+        <v>8.642029523849487</v>
       </c>
       <c r="F15" t="n">
-        <v>8.186137199401855</v>
+        <v>6.675438404083252</v>
       </c>
       <c r="G15" t="n">
-        <v>7.116366624832153</v>
+        <v>7.194308280944824</v>
       </c>
       <c r="H15" t="n">
-        <v>8.694336414337158</v>
+        <v>8.774729251861572</v>
       </c>
       <c r="I15" t="n">
-        <v>7.677434682846069</v>
+        <v>7.268646001815796</v>
       </c>
       <c r="J15" t="n">
-        <v>8.705299615859985</v>
+        <v>7.449628829956055</v>
       </c>
       <c r="K15" t="n">
-        <v>7.138083696365356</v>
+        <v>6.953796625137329</v>
       </c>
       <c r="L15" t="n">
-        <v>7.786740565299988</v>
+        <v>7.599422883987427</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.579764842987061</v>
+        <v>6.723896265029907</v>
       </c>
       <c r="C16" t="n">
-        <v>6.62877345085144</v>
+        <v>7.740826845169067</v>
       </c>
       <c r="D16" t="n">
-        <v>10.60834240913391</v>
+        <v>7.228596210479736</v>
       </c>
       <c r="E16" t="n">
-        <v>7.280558109283447</v>
+        <v>7.308944940567017</v>
       </c>
       <c r="F16" t="n">
-        <v>6.76686954498291</v>
+        <v>6.163818597793579</v>
       </c>
       <c r="G16" t="n">
-        <v>7.032897710800171</v>
+        <v>8.473297595977783</v>
       </c>
       <c r="H16" t="n">
-        <v>7.247622013092041</v>
+        <v>6.69144344329834</v>
       </c>
       <c r="I16" t="n">
-        <v>6.811251640319824</v>
+        <v>6.949809789657593</v>
       </c>
       <c r="J16" t="n">
-        <v>7.488547801971436</v>
+        <v>6.742334842681885</v>
       </c>
       <c r="K16" t="n">
-        <v>7.162044286727905</v>
+        <v>7.225628614425659</v>
       </c>
       <c r="L16" t="n">
-        <v>7.460667181015014</v>
+        <v>7.124859714508057</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.456003189086914</v>
+        <v>9.567164659500122</v>
       </c>
       <c r="C17" t="n">
-        <v>7.477449655532837</v>
+        <v>7.123390436172485</v>
       </c>
       <c r="D17" t="n">
-        <v>7.458004236221313</v>
+        <v>7.958229780197144</v>
       </c>
       <c r="E17" t="n">
-        <v>7.455515384674072</v>
+        <v>7.412205696105957</v>
       </c>
       <c r="F17" t="n">
-        <v>7.620567798614502</v>
+        <v>7.457540512084961</v>
       </c>
       <c r="G17" t="n">
-        <v>7.74775242805481</v>
+        <v>6.70941162109375</v>
       </c>
       <c r="H17" t="n">
-        <v>10.31323146820068</v>
+        <v>9.522533893585205</v>
       </c>
       <c r="I17" t="n">
-        <v>7.414119958877563</v>
+        <v>6.793705224990845</v>
       </c>
       <c r="J17" t="n">
-        <v>7.273847103118896</v>
+        <v>7.492443323135376</v>
       </c>
       <c r="K17" t="n">
-        <v>8.483576059341431</v>
+        <v>6.908434629440308</v>
       </c>
       <c r="L17" t="n">
-        <v>7.870006728172302</v>
+        <v>7.694505977630615</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>7.878428936004639</v>
+        <v>8.100419759750366</v>
       </c>
       <c r="C18" t="n">
-        <v>6.657028913497925</v>
+        <v>6.966325998306274</v>
       </c>
       <c r="D18" t="n">
-        <v>6.744813203811646</v>
+        <v>6.637094259262085</v>
       </c>
       <c r="E18" t="n">
-        <v>6.513871669769287</v>
+        <v>6.806679487228394</v>
       </c>
       <c r="F18" t="n">
-        <v>6.731358528137207</v>
+        <v>7.046099662780762</v>
       </c>
       <c r="G18" t="n">
-        <v>6.911919116973877</v>
+        <v>6.54237699508667</v>
       </c>
       <c r="H18" t="n">
-        <v>6.89790940284729</v>
+        <v>6.561768770217896</v>
       </c>
       <c r="I18" t="n">
-        <v>7.095930099487305</v>
+        <v>7.282954454421997</v>
       </c>
       <c r="J18" t="n">
-        <v>10.18666219711304</v>
+        <v>6.543834686279297</v>
       </c>
       <c r="K18" t="n">
-        <v>6.595231771469116</v>
+        <v>6.859064340591431</v>
       </c>
       <c r="L18" t="n">
-        <v>7.221315383911133</v>
+        <v>6.934661841392517</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>8.472416400909424</v>
+        <v>6.570854902267456</v>
       </c>
       <c r="C19" t="n">
-        <v>6.361779928207397</v>
+        <v>7.69832181930542</v>
       </c>
       <c r="D19" t="n">
-        <v>6.678492069244385</v>
+        <v>6.538524627685547</v>
       </c>
       <c r="E19" t="n">
-        <v>6.256063461303711</v>
+        <v>8.289077520370483</v>
       </c>
       <c r="F19" t="n">
-        <v>8.292375326156616</v>
+        <v>8.46757173538208</v>
       </c>
       <c r="G19" t="n">
-        <v>6.516545534133911</v>
+        <v>8.002777576446533</v>
       </c>
       <c r="H19" t="n">
-        <v>6.505581140518188</v>
+        <v>8.335367679595947</v>
       </c>
       <c r="I19" t="n">
-        <v>8.258509635925293</v>
+        <v>7.489538908004761</v>
       </c>
       <c r="J19" t="n">
-        <v>6.743958234786987</v>
+        <v>8.234709978103638</v>
       </c>
       <c r="K19" t="n">
-        <v>8.255027055740356</v>
+        <v>7.239615440368652</v>
       </c>
       <c r="L19" t="n">
-        <v>7.234074878692627</v>
+        <v>7.686636018753052</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>9.177111625671387</v>
+        <v>6.914916515350342</v>
       </c>
       <c r="C20" t="n">
-        <v>7.105018854141235</v>
+        <v>9.893397808074951</v>
       </c>
       <c r="D20" t="n">
-        <v>8.825038194656372</v>
+        <v>8.480444192886353</v>
       </c>
       <c r="E20" t="n">
-        <v>9.091347217559814</v>
+        <v>6.747853755950928</v>
       </c>
       <c r="F20" t="n">
-        <v>8.579704523086548</v>
+        <v>9.524121284484863</v>
       </c>
       <c r="G20" t="n">
-        <v>7.155895471572876</v>
+        <v>8.803195238113403</v>
       </c>
       <c r="H20" t="n">
-        <v>9.060931921005249</v>
+        <v>7.08948802947998</v>
       </c>
       <c r="I20" t="n">
-        <v>9.090339422225952</v>
+        <v>9.231520414352417</v>
       </c>
       <c r="J20" t="n">
-        <v>7.491021394729614</v>
+        <v>7.318908214569092</v>
       </c>
       <c r="K20" t="n">
-        <v>8.645483016967773</v>
+        <v>7.197667598724365</v>
       </c>
       <c r="L20" t="n">
-        <v>8.422189164161683</v>
+        <v>8.12015130519867</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.363833904266357</v>
+        <v>7.013476371765137</v>
       </c>
       <c r="C21" t="n">
-        <v>8.44501781463623</v>
+        <v>6.689515352249146</v>
       </c>
       <c r="D21" t="n">
-        <v>6.969880104064941</v>
+        <v>7.181730985641479</v>
       </c>
       <c r="E21" t="n">
-        <v>6.876103162765503</v>
+        <v>7.2286376953125</v>
       </c>
       <c r="F21" t="n">
-        <v>8.01513409614563</v>
+        <v>6.601210832595825</v>
       </c>
       <c r="G21" t="n">
-        <v>6.958920955657959</v>
+        <v>8.985692501068115</v>
       </c>
       <c r="H21" t="n">
-        <v>8.699389934539795</v>
+        <v>7.731884956359863</v>
       </c>
       <c r="I21" t="n">
-        <v>6.80427885055542</v>
+        <v>8.914953231811523</v>
       </c>
       <c r="J21" t="n">
-        <v>8.208671808242798</v>
+        <v>8.786726951599121</v>
       </c>
       <c r="K21" t="n">
-        <v>8.376589059829712</v>
+        <v>8.622050762176514</v>
       </c>
       <c r="L21" t="n">
-        <v>7.671781969070435</v>
+        <v>7.775587964057922</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.016671180725098</v>
+        <v>6.468650102615356</v>
       </c>
       <c r="C22" t="n">
-        <v>7.016119241714478</v>
+        <v>6.475061893463135</v>
       </c>
       <c r="D22" t="n">
-        <v>6.9582679271698</v>
+        <v>6.921898603439331</v>
       </c>
       <c r="E22" t="n">
-        <v>6.369276762008667</v>
+        <v>6.378282070159912</v>
       </c>
       <c r="F22" t="n">
-        <v>6.503932952880859</v>
+        <v>7.233104467391968</v>
       </c>
       <c r="G22" t="n">
-        <v>8.226062297821045</v>
+        <v>7.088958263397217</v>
       </c>
       <c r="H22" t="n">
-        <v>6.508410692214966</v>
+        <v>5.703998327255249</v>
       </c>
       <c r="I22" t="n">
-        <v>6.835657835006714</v>
+        <v>7.731863021850586</v>
       </c>
       <c r="J22" t="n">
-        <v>6.042588472366333</v>
+        <v>7.197747230529785</v>
       </c>
       <c r="K22" t="n">
-        <v>6.786741733551025</v>
+        <v>6.500125646591187</v>
       </c>
       <c r="L22" t="n">
-        <v>6.726372909545899</v>
+        <v>6.769968962669372</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.558200120925903</v>
+        <v>8.029302597045898</v>
       </c>
       <c r="C23" t="n">
-        <v>8.420576095581055</v>
+        <v>8.977174282073975</v>
       </c>
       <c r="D23" t="n">
-        <v>8.792583703994751</v>
+        <v>7.8719801902771</v>
       </c>
       <c r="E23" t="n">
-        <v>8.890310049057007</v>
+        <v>7.743897676467896</v>
       </c>
       <c r="F23" t="n">
-        <v>9.367120981216431</v>
+        <v>7.203663349151611</v>
       </c>
       <c r="G23" t="n">
-        <v>8.338262319564819</v>
+        <v>8.968654155731201</v>
       </c>
       <c r="H23" t="n">
-        <v>9.841897010803223</v>
+        <v>9.048979759216309</v>
       </c>
       <c r="I23" t="n">
-        <v>8.774621725082397</v>
+        <v>8.255500793457031</v>
       </c>
       <c r="J23" t="n">
-        <v>8.346246719360352</v>
+        <v>9.832039833068848</v>
       </c>
       <c r="K23" t="n">
-        <v>9.737705707550049</v>
+        <v>8.753260612487793</v>
       </c>
       <c r="L23" t="n">
-        <v>8.906752443313598</v>
+        <v>8.468445324897766</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>9.484317064285278</v>
+        <v>9.369194507598877</v>
       </c>
       <c r="C24" t="n">
-        <v>7.654474496841431</v>
+        <v>7.403157234191895</v>
       </c>
       <c r="D24" t="n">
-        <v>8.738201141357422</v>
+        <v>9.066947221755981</v>
       </c>
       <c r="E24" t="n">
-        <v>7.092445135116577</v>
+        <v>9.772183179855347</v>
       </c>
       <c r="F24" t="n">
-        <v>10.20201635360718</v>
+        <v>7.52356481552124</v>
       </c>
       <c r="G24" t="n">
-        <v>9.203819036483765</v>
+        <v>6.611827850341797</v>
       </c>
       <c r="H24" t="n">
-        <v>8.547241687774658</v>
+        <v>9.762156248092651</v>
       </c>
       <c r="I24" t="n">
-        <v>9.546644449234009</v>
+        <v>9.982062816619873</v>
       </c>
       <c r="J24" t="n">
-        <v>8.191815137863159</v>
+        <v>8.962206840515137</v>
       </c>
       <c r="K24" t="n">
-        <v>9.032516002655029</v>
+        <v>9.921890735626221</v>
       </c>
       <c r="L24" t="n">
-        <v>8.76934905052185</v>
+        <v>8.837519145011902</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>8.946228265762329</v>
+        <v>8.042575836181641</v>
       </c>
       <c r="C25" t="n">
-        <v>6.7474524974823</v>
+        <v>7.116400241851807</v>
       </c>
       <c r="D25" t="n">
-        <v>7.617686748504639</v>
+        <v>7.515376329421997</v>
       </c>
       <c r="E25" t="n">
-        <v>7.780671834945679</v>
+        <v>6.585243225097656</v>
       </c>
       <c r="F25" t="n">
-        <v>7.302883386611938</v>
+        <v>7.140356540679932</v>
       </c>
       <c r="G25" t="n">
-        <v>9.166621923446655</v>
+        <v>7.358293771743774</v>
       </c>
       <c r="H25" t="n">
-        <v>10.09928607940674</v>
+        <v>6.620157718658447</v>
       </c>
       <c r="I25" t="n">
-        <v>7.747294664382935</v>
+        <v>6.723382949829102</v>
       </c>
       <c r="J25" t="n">
-        <v>9.024341106414795</v>
+        <v>7.325896978378296</v>
       </c>
       <c r="K25" t="n">
-        <v>7.611690759658813</v>
+        <v>7.101434946060181</v>
       </c>
       <c r="L25" t="n">
-        <v>8.204415726661683</v>
+        <v>7.152911853790283</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>6.301097631454468</v>
+        <v>6.15434718132019</v>
       </c>
       <c r="C26" t="n">
-        <v>8.805717945098877</v>
+        <v>7.009972810745239</v>
       </c>
       <c r="D26" t="n">
-        <v>8.720243692398071</v>
+        <v>6.661216735839844</v>
       </c>
       <c r="E26" t="n">
-        <v>6.888440132141113</v>
+        <v>6.525532960891724</v>
       </c>
       <c r="F26" t="n">
-        <v>6.686460494995117</v>
+        <v>7.73739218711853</v>
       </c>
       <c r="G26" t="n">
-        <v>8.748231410980225</v>
+        <v>8.141344308853149</v>
       </c>
       <c r="H26" t="n">
-        <v>6.80667519569397</v>
+        <v>6.455721139907837</v>
       </c>
       <c r="I26" t="n">
-        <v>7.005193471908569</v>
+        <v>6.654742002487183</v>
       </c>
       <c r="J26" t="n">
-        <v>6.427621126174927</v>
+        <v>6.812300205230713</v>
       </c>
       <c r="K26" t="n">
-        <v>6.876981496810913</v>
+        <v>7.084108114242554</v>
       </c>
       <c r="L26" t="n">
-        <v>7.326666259765625</v>
+        <v>6.923667764663696</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>10.27578973770142</v>
+        <v>8.853014945983887</v>
       </c>
       <c r="C27" t="n">
-        <v>9.447065353393555</v>
+        <v>8.098817825317383</v>
       </c>
       <c r="D27" t="n">
-        <v>7.657984733581543</v>
+        <v>9.074433565139771</v>
       </c>
       <c r="E27" t="n">
-        <v>8.516802310943604</v>
+        <v>7.223610639572144</v>
       </c>
       <c r="F27" t="n">
-        <v>7.235636711120605</v>
+        <v>9.593644142150879</v>
       </c>
       <c r="G27" t="n">
-        <v>9.657391309738159</v>
+        <v>7.105949878692627</v>
       </c>
       <c r="H27" t="n">
-        <v>9.729693651199341</v>
+        <v>7.247054576873779</v>
       </c>
       <c r="I27" t="n">
-        <v>8.856925010681152</v>
+        <v>9.360658168792725</v>
       </c>
       <c r="J27" t="n">
-        <v>7.269050598144531</v>
+        <v>6.658636331558228</v>
       </c>
       <c r="K27" t="n">
-        <v>7.887437343597412</v>
+        <v>7.098950624465942</v>
       </c>
       <c r="L27" t="n">
-        <v>8.653377676010132</v>
+        <v>8.031477069854736</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.822062492370605</v>
+        <v>7.842061042785645</v>
       </c>
       <c r="C28" t="n">
-        <v>10.14866733551025</v>
+        <v>7.247996091842651</v>
       </c>
       <c r="D28" t="n">
-        <v>7.690994262695312</v>
+        <v>7.948796272277832</v>
       </c>
       <c r="E28" t="n">
-        <v>7.686924934387207</v>
+        <v>9.006618738174438</v>
       </c>
       <c r="F28" t="n">
-        <v>9.318787574768066</v>
+        <v>6.702472925186157</v>
       </c>
       <c r="G28" t="n">
-        <v>7.263452053070068</v>
+        <v>7.355285882949829</v>
       </c>
       <c r="H28" t="n">
-        <v>9.478352785110474</v>
+        <v>7.716863870620728</v>
       </c>
       <c r="I28" t="n">
-        <v>7.130369901657104</v>
+        <v>6.96066427230835</v>
       </c>
       <c r="J28" t="n">
-        <v>7.549264669418335</v>
+        <v>8.132357358932495</v>
       </c>
       <c r="K28" t="n">
-        <v>10.39152550697327</v>
+        <v>7.483059883117676</v>
       </c>
       <c r="L28" t="n">
-        <v>8.44804015159607</v>
+        <v>7.63961763381958</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>9.538219213485718</v>
+        <v>8.70688271522522</v>
       </c>
       <c r="C29" t="n">
-        <v>8.598124265670776</v>
+        <v>7.998251914978027</v>
       </c>
       <c r="D29" t="n">
-        <v>7.323742389678955</v>
+        <v>9.894784212112427</v>
       </c>
       <c r="E29" t="n">
-        <v>7.40810227394104</v>
+        <v>9.213096618652344</v>
       </c>
       <c r="F29" t="n">
-        <v>8.657944917678833</v>
+        <v>9.203605175018311</v>
       </c>
       <c r="G29" t="n">
-        <v>8.561205625534058</v>
+        <v>8.368338584899902</v>
       </c>
       <c r="H29" t="n">
-        <v>9.311256170272827</v>
+        <v>8.442050218582153</v>
       </c>
       <c r="I29" t="n">
-        <v>9.583588600158691</v>
+        <v>7.396783351898193</v>
       </c>
       <c r="J29" t="n">
-        <v>7.195679426193237</v>
+        <v>9.586065053939819</v>
       </c>
       <c r="K29" t="n">
-        <v>7.985172510147095</v>
+        <v>8.890902757644653</v>
       </c>
       <c r="L29" t="n">
-        <v>8.416303539276123</v>
+        <v>8.770076060295105</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>8.256959676742554</v>
+        <v>7.043723106384277</v>
       </c>
       <c r="C30" t="n">
-        <v>9.301790952682495</v>
+        <v>7.140975952148438</v>
       </c>
       <c r="D30" t="n">
-        <v>7.069993495941162</v>
+        <v>7.211393594741821</v>
       </c>
       <c r="E30" t="n">
-        <v>7.173732995986938</v>
+        <v>9.647436618804932</v>
       </c>
       <c r="F30" t="n">
-        <v>10.12170815467834</v>
+        <v>8.899855375289917</v>
       </c>
       <c r="G30" t="n">
-        <v>7.509357452392578</v>
+        <v>7.282015085220337</v>
       </c>
       <c r="H30" t="n">
-        <v>8.654928684234619</v>
+        <v>7.864555358886719</v>
       </c>
       <c r="I30" t="n">
-        <v>9.55513072013855</v>
+        <v>8.644542932510376</v>
       </c>
       <c r="J30" t="n">
-        <v>10.36451840400696</v>
+        <v>8.928828716278076</v>
       </c>
       <c r="K30" t="n">
-        <v>8.010172128677368</v>
+        <v>7.892483234405518</v>
       </c>
       <c r="L30" t="n">
-        <v>8.601829266548156</v>
+        <v>8.055580997467041</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.447033166885376</v>
+        <v>6.373953104019165</v>
       </c>
       <c r="C31" t="n">
-        <v>8.867412805557251</v>
+        <v>6.823265790939331</v>
       </c>
       <c r="D31" t="n">
-        <v>7.085548877716064</v>
+        <v>7.449174165725708</v>
       </c>
       <c r="E31" t="n">
-        <v>8.358228921890259</v>
+        <v>8.632559299468994</v>
       </c>
       <c r="F31" t="n">
-        <v>6.925487279891968</v>
+        <v>9.360497951507568</v>
       </c>
       <c r="G31" t="n">
-        <v>6.78583025932312</v>
+        <v>6.433274030685425</v>
       </c>
       <c r="H31" t="n">
-        <v>7.50693941116333</v>
+        <v>9.007620334625244</v>
       </c>
       <c r="I31" t="n">
-        <v>10.51114416122437</v>
+        <v>6.420315980911255</v>
       </c>
       <c r="J31" t="n">
-        <v>9.8101966381073</v>
+        <v>10.59252691268921</v>
       </c>
       <c r="K31" t="n">
-        <v>6.944863796234131</v>
+        <v>7.314540147781372</v>
       </c>
       <c r="L31" t="n">
-        <v>8.124268531799316</v>
+        <v>7.840772771835328</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.574182033538818</v>
+        <v>8.401169776916504</v>
       </c>
       <c r="C32" t="n">
-        <v>6.622181415557861</v>
+        <v>7.628174304962158</v>
       </c>
       <c r="D32" t="n">
-        <v>9.667493104934692</v>
+        <v>6.581889390945435</v>
       </c>
       <c r="E32" t="n">
-        <v>6.35993480682373</v>
+        <v>6.683652400970459</v>
       </c>
       <c r="F32" t="n">
-        <v>6.64069938659668</v>
+        <v>6.500608205795288</v>
       </c>
       <c r="G32" t="n">
-        <v>8.384208202362061</v>
+        <v>6.358504772186279</v>
       </c>
       <c r="H32" t="n">
-        <v>8.172214508056641</v>
+        <v>8.249564170837402</v>
       </c>
       <c r="I32" t="n">
-        <v>6.141936302185059</v>
+        <v>6.814301490783691</v>
       </c>
       <c r="J32" t="n">
-        <v>9.668358087539673</v>
+        <v>6.539511919021606</v>
       </c>
       <c r="K32" t="n">
-        <v>8.494865894317627</v>
+        <v>8.953727245330811</v>
       </c>
       <c r="L32" t="n">
-        <v>7.872607374191285</v>
+        <v>7.271110367774964</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.189697504043579</v>
+        <v>7.51198673248291</v>
       </c>
       <c r="C33" t="n">
-        <v>9.119872570037842</v>
+        <v>7.335430145263672</v>
       </c>
       <c r="D33" t="n">
-        <v>13.25094294548035</v>
+        <v>7.195301532745361</v>
       </c>
       <c r="E33" t="n">
-        <v>9.824590921401978</v>
+        <v>8.104935646057129</v>
       </c>
       <c r="F33" t="n">
-        <v>9.34344744682312</v>
+        <v>7.936856269836426</v>
       </c>
       <c r="G33" t="n">
-        <v>9.485151529312134</v>
+        <v>6.475185632705688</v>
       </c>
       <c r="H33" t="n">
-        <v>8.127406597137451</v>
+        <v>7.27762508392334</v>
       </c>
       <c r="I33" t="n">
-        <v>7.66299843788147</v>
+        <v>6.719038009643555</v>
       </c>
       <c r="J33" t="n">
-        <v>8.421931982040405</v>
+        <v>6.884618282318115</v>
       </c>
       <c r="K33" t="n">
-        <v>8.923709869384766</v>
+        <v>6.692786455154419</v>
       </c>
       <c r="L33" t="n">
-        <v>9.134974980354309</v>
+        <v>7.213376379013061</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>9.433019876480103</v>
+        <v>6.514933109283447</v>
       </c>
       <c r="C34" t="n">
-        <v>8.351065158843994</v>
+        <v>7.602672815322876</v>
       </c>
       <c r="D34" t="n">
-        <v>9.633873224258423</v>
+        <v>6.262067556381226</v>
       </c>
       <c r="E34" t="n">
-        <v>9.244390249252319</v>
+        <v>8.06898307800293</v>
       </c>
       <c r="F34" t="n">
-        <v>6.735471248626709</v>
+        <v>8.747311353683472</v>
       </c>
       <c r="G34" t="n">
-        <v>8.912513017654419</v>
+        <v>6.325448513031006</v>
       </c>
       <c r="H34" t="n">
-        <v>8.710061073303223</v>
+        <v>7.436071395874023</v>
       </c>
       <c r="I34" t="n">
-        <v>6.936343431472778</v>
+        <v>6.377787113189697</v>
       </c>
       <c r="J34" t="n">
-        <v>7.048694849014282</v>
+        <v>7.526375293731689</v>
       </c>
       <c r="K34" t="n">
-        <v>7.783058881759644</v>
+        <v>7.752872467041016</v>
       </c>
       <c r="L34" t="n">
-        <v>8.278849101066589</v>
+        <v>7.261452269554138</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.837326765060425</v>
+        <v>9.10979437828064</v>
       </c>
       <c r="C35" t="n">
-        <v>7.827247142791748</v>
+        <v>7.141706466674805</v>
       </c>
       <c r="D35" t="n">
-        <v>8.004367351531982</v>
+        <v>8.032578468322754</v>
       </c>
       <c r="E35" t="n">
-        <v>7.122805118560791</v>
+        <v>7.36278223991394</v>
       </c>
       <c r="F35" t="n">
-        <v>7.661511898040771</v>
+        <v>7.994653463363647</v>
       </c>
       <c r="G35" t="n">
-        <v>7.738837718963623</v>
+        <v>7.580763101577759</v>
       </c>
       <c r="H35" t="n">
-        <v>7.555383682250977</v>
+        <v>7.178243398666382</v>
       </c>
       <c r="I35" t="n">
-        <v>8.758450269699097</v>
+        <v>8.417617797851562</v>
       </c>
       <c r="J35" t="n">
-        <v>7.23154091835022</v>
+        <v>7.388268709182739</v>
       </c>
       <c r="K35" t="n">
-        <v>7.567795515060425</v>
+        <v>7.543296337127686</v>
       </c>
       <c r="L35" t="n">
-        <v>7.730526638031006</v>
+        <v>7.774970436096192</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.594115018844604</v>
+        <v>10.61603498458862</v>
       </c>
       <c r="C36" t="n">
-        <v>7.947806119918823</v>
+        <v>9.36719799041748</v>
       </c>
       <c r="D36" t="n">
-        <v>8.585592985153198</v>
+        <v>9.346737146377563</v>
       </c>
       <c r="E36" t="n">
-        <v>8.440608024597168</v>
+        <v>8.788631916046143</v>
       </c>
       <c r="F36" t="n">
-        <v>8.627353668212891</v>
+        <v>8.060187101364136</v>
       </c>
       <c r="G36" t="n">
-        <v>9.774412393569946</v>
+        <v>9.247939109802246</v>
       </c>
       <c r="H36" t="n">
-        <v>6.818418502807617</v>
+        <v>7.486140489578247</v>
       </c>
       <c r="I36" t="n">
-        <v>9.080840349197388</v>
+        <v>10.07437491416931</v>
       </c>
       <c r="J36" t="n">
-        <v>7.628770589828491</v>
+        <v>7.466561794281006</v>
       </c>
       <c r="K36" t="n">
-        <v>9.734262704849243</v>
+        <v>7.773833036422729</v>
       </c>
       <c r="L36" t="n">
-        <v>8.523218035697937</v>
+        <v>8.822763848304749</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>6.464632987976074</v>
+        <v>6.679618358612061</v>
       </c>
       <c r="C37" t="n">
-        <v>7.266538619995117</v>
+        <v>7.430243015289307</v>
       </c>
       <c r="D37" t="n">
-        <v>6.387872219085693</v>
+        <v>6.241782903671265</v>
       </c>
       <c r="E37" t="n">
-        <v>5.97709321975708</v>
+        <v>6.552482128143311</v>
       </c>
       <c r="F37" t="n">
-        <v>5.96471905708313</v>
+        <v>6.033083438873291</v>
       </c>
       <c r="G37" t="n">
-        <v>6.445833921432495</v>
+        <v>7.636754989624023</v>
       </c>
       <c r="H37" t="n">
-        <v>6.720980882644653</v>
+        <v>7.331857442855835</v>
       </c>
       <c r="I37" t="n">
-        <v>6.261025905609131</v>
+        <v>6.514924764633179</v>
       </c>
       <c r="J37" t="n">
-        <v>9.02773642539978</v>
+        <v>5.726953029632568</v>
       </c>
       <c r="K37" t="n">
-        <v>6.53046441078186</v>
+        <v>6.819643497467041</v>
       </c>
       <c r="L37" t="n">
-        <v>6.704689764976502</v>
+        <v>6.696734356880188</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.701347589492798</v>
+        <v>7.899987697601318</v>
       </c>
       <c r="C38" t="n">
-        <v>7.009722471237183</v>
+        <v>9.443985223770142</v>
       </c>
       <c r="D38" t="n">
-        <v>7.060625791549683</v>
+        <v>6.363834619522095</v>
       </c>
       <c r="E38" t="n">
-        <v>6.364552736282349</v>
+        <v>6.729434728622437</v>
       </c>
       <c r="F38" t="n">
-        <v>6.518967390060425</v>
+        <v>6.947814464569092</v>
       </c>
       <c r="G38" t="n">
-        <v>7.673646926879883</v>
+        <v>6.89957594871521</v>
       </c>
       <c r="H38" t="n">
-        <v>8.639999866485596</v>
+        <v>6.326059103012085</v>
       </c>
       <c r="I38" t="n">
-        <v>7.277985095977783</v>
+        <v>9.247958660125732</v>
       </c>
       <c r="J38" t="n">
-        <v>9.135268926620483</v>
+        <v>6.62279224395752</v>
       </c>
       <c r="K38" t="n">
-        <v>8.449710369110107</v>
+        <v>8.398171663284302</v>
       </c>
       <c r="L38" t="n">
-        <v>7.483182716369629</v>
+        <v>7.487961435317994</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>6.466903924942017</v>
+        <v>6.268238544464111</v>
       </c>
       <c r="C39" t="n">
-        <v>6.024443387985229</v>
+        <v>6.665688514709473</v>
       </c>
       <c r="D39" t="n">
-        <v>7.446216821670532</v>
+        <v>6.986812114715576</v>
       </c>
       <c r="E39" t="n">
-        <v>8.642975807189941</v>
+        <v>6.914535284042358</v>
       </c>
       <c r="F39" t="n">
-        <v>7.701769828796387</v>
+        <v>6.209854125976562</v>
       </c>
       <c r="G39" t="n">
-        <v>6.519170999526978</v>
+        <v>6.85019850730896</v>
       </c>
       <c r="H39" t="n">
-        <v>8.1678307056427</v>
+        <v>9.096909284591675</v>
       </c>
       <c r="I39" t="n">
-        <v>7.782151460647583</v>
+        <v>7.066191434860229</v>
       </c>
       <c r="J39" t="n">
-        <v>7.464200258255005</v>
+        <v>8.16427755355835</v>
       </c>
       <c r="K39" t="n">
-        <v>8.880856275558472</v>
+        <v>9.71824312210083</v>
       </c>
       <c r="L39" t="n">
-        <v>7.509651947021484</v>
+        <v>7.394094848632813</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.261480331420898</v>
+        <v>8.977697610855103</v>
       </c>
       <c r="C40" t="n">
-        <v>6.658071517944336</v>
+        <v>6.5644371509552</v>
       </c>
       <c r="D40" t="n">
-        <v>6.461949586868286</v>
+        <v>7.084078311920166</v>
       </c>
       <c r="E40" t="n">
-        <v>6.551051139831543</v>
+        <v>7.000827789306641</v>
       </c>
       <c r="F40" t="n">
-        <v>7.579402923583984</v>
+        <v>8.423120975494385</v>
       </c>
       <c r="G40" t="n">
-        <v>9.131524801254272</v>
+        <v>7.249260902404785</v>
       </c>
       <c r="H40" t="n">
-        <v>7.105894565582275</v>
+        <v>8.477449417114258</v>
       </c>
       <c r="I40" t="n">
-        <v>6.851576566696167</v>
+        <v>7.141966342926025</v>
       </c>
       <c r="J40" t="n">
-        <v>8.175388336181641</v>
+        <v>7.265646696090698</v>
       </c>
       <c r="K40" t="n">
-        <v>7.425908327102661</v>
+        <v>6.351974725723267</v>
       </c>
       <c r="L40" t="n">
-        <v>7.320224809646606</v>
+        <v>7.453645992279053</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.873544692993164</v>
+        <v>9.526733875274658</v>
       </c>
       <c r="C41" t="n">
-        <v>7.150012493133545</v>
+        <v>8.104910373687744</v>
       </c>
       <c r="D41" t="n">
-        <v>7.467513561248779</v>
+        <v>9.04550576210022</v>
       </c>
       <c r="E41" t="n">
-        <v>8.948952198028564</v>
+        <v>8.954245328903198</v>
       </c>
       <c r="F41" t="n">
-        <v>7.862666845321655</v>
+        <v>7.76486349105835</v>
       </c>
       <c r="G41" t="n">
-        <v>7.66942286491394</v>
+        <v>9.724234819412231</v>
       </c>
       <c r="H41" t="n">
-        <v>8.017011165618896</v>
+        <v>10.36710143089294</v>
       </c>
       <c r="I41" t="n">
-        <v>7.776946067810059</v>
+        <v>9.849939346313477</v>
       </c>
       <c r="J41" t="n">
-        <v>8.117885589599609</v>
+        <v>9.135047912597656</v>
       </c>
       <c r="K41" t="n">
-        <v>7.697355031967163</v>
+        <v>8.002690315246582</v>
       </c>
       <c r="L41" t="n">
-        <v>7.858131051063538</v>
+        <v>9.047527265548705</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.856781244277954</v>
+        <v>5.788979530334473</v>
       </c>
       <c r="C42" t="n">
-        <v>5.782134771347046</v>
+        <v>5.892678499221802</v>
       </c>
       <c r="D42" t="n">
-        <v>5.364606857299805</v>
+        <v>5.922162294387817</v>
       </c>
       <c r="E42" t="n">
-        <v>5.915977001190186</v>
+        <v>5.389439344406128</v>
       </c>
       <c r="F42" t="n">
-        <v>6.037440776824951</v>
+        <v>5.92298412322998</v>
       </c>
       <c r="G42" t="n">
-        <v>5.702864408493042</v>
+        <v>7.928885698318481</v>
       </c>
       <c r="H42" t="n">
-        <v>5.680103778839111</v>
+        <v>5.739083051681519</v>
       </c>
       <c r="I42" t="n">
-        <v>6.929979085922241</v>
+        <v>6.000397682189941</v>
       </c>
       <c r="J42" t="n">
-        <v>6.434504270553589</v>
+        <v>5.509686946868896</v>
       </c>
       <c r="K42" t="n">
-        <v>6.875314712524414</v>
+        <v>5.703231334686279</v>
       </c>
       <c r="L42" t="n">
-        <v>6.057970690727234</v>
+        <v>5.979752850532532</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.662010908126831</v>
+        <v>6.340008974075317</v>
       </c>
       <c r="C43" t="n">
-        <v>7.992924928665161</v>
+        <v>8.462990045547485</v>
       </c>
       <c r="D43" t="n">
-        <v>6.163810014724731</v>
+        <v>8.08053994178772</v>
       </c>
       <c r="E43" t="n">
-        <v>7.941832542419434</v>
+        <v>6.246797800064087</v>
       </c>
       <c r="F43" t="n">
-        <v>8.034761190414429</v>
+        <v>7.636121988296509</v>
       </c>
       <c r="G43" t="n">
-        <v>8.027145147323608</v>
+        <v>8.101454257965088</v>
       </c>
       <c r="H43" t="n">
-        <v>7.829972267150879</v>
+        <v>7.346950054168701</v>
       </c>
       <c r="I43" t="n">
-        <v>6.36259651184082</v>
+        <v>7.579786062240601</v>
       </c>
       <c r="J43" t="n">
-        <v>6.742647409439087</v>
+        <v>7.136958122253418</v>
       </c>
       <c r="K43" t="n">
-        <v>6.45160984992981</v>
+        <v>8.570747137069702</v>
       </c>
       <c r="L43" t="n">
-        <v>7.220931077003479</v>
+        <v>7.550235438346863</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>8.591502666473389</v>
+        <v>9.03559684753418</v>
       </c>
       <c r="C44" t="n">
-        <v>7.680664300918579</v>
+        <v>7.846626043319702</v>
       </c>
       <c r="D44" t="n">
-        <v>7.102967977523804</v>
+        <v>8.478480815887451</v>
       </c>
       <c r="E44" t="n">
-        <v>7.376343727111816</v>
+        <v>7.098626136779785</v>
       </c>
       <c r="F44" t="n">
-        <v>6.35810375213623</v>
+        <v>6.770304679870605</v>
       </c>
       <c r="G44" t="n">
-        <v>8.548198699951172</v>
+        <v>7.796146631240845</v>
       </c>
       <c r="H44" t="n">
-        <v>6.319355726242065</v>
+        <v>8.648491382598877</v>
       </c>
       <c r="I44" t="n">
-        <v>7.075507879257202</v>
+        <v>7.348834991455078</v>
       </c>
       <c r="J44" t="n">
-        <v>7.063496351242065</v>
+        <v>7.071009159088135</v>
       </c>
       <c r="K44" t="n">
-        <v>7.081429004669189</v>
+        <v>6.287497758865356</v>
       </c>
       <c r="L44" t="n">
-        <v>7.319757008552552</v>
+        <v>7.638161444664002</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>7.198706865310669</v>
+        <v>6.783742189407349</v>
       </c>
       <c r="C45" t="n">
-        <v>7.9149329662323</v>
+        <v>8.689399242401123</v>
       </c>
       <c r="D45" t="n">
-        <v>7.482927560806274</v>
+        <v>7.704930305480957</v>
       </c>
       <c r="E45" t="n">
-        <v>7.652036190032959</v>
+        <v>8.799653053283691</v>
       </c>
       <c r="F45" t="n">
-        <v>7.168425559997559</v>
+        <v>9.517128705978394</v>
       </c>
       <c r="G45" t="n">
-        <v>7.165124177932739</v>
+        <v>8.241545677185059</v>
       </c>
       <c r="H45" t="n">
-        <v>9.465466499328613</v>
+        <v>7.005930185317993</v>
       </c>
       <c r="I45" t="n">
-        <v>9.187631607055664</v>
+        <v>9.207059860229492</v>
       </c>
       <c r="J45" t="n">
-        <v>7.428722381591797</v>
+        <v>8.806164503097534</v>
       </c>
       <c r="K45" t="n">
-        <v>7.715953826904297</v>
+        <v>10.58051466941833</v>
       </c>
       <c r="L45" t="n">
-        <v>7.837992763519287</v>
+        <v>8.533606839179992</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>6.934142351150513</v>
+        <v>8.367793560028076</v>
       </c>
       <c r="C46" t="n">
-        <v>9.672574996948242</v>
+        <v>7.101441144943237</v>
       </c>
       <c r="D46" t="n">
-        <v>7.353367567062378</v>
+        <v>6.877702713012695</v>
       </c>
       <c r="E46" t="n">
-        <v>6.65309739112854</v>
+        <v>8.108944654464722</v>
       </c>
       <c r="F46" t="n">
-        <v>7.076986789703369</v>
+        <v>8.464973211288452</v>
       </c>
       <c r="G46" t="n">
-        <v>6.599783182144165</v>
+        <v>7.070003032684326</v>
       </c>
       <c r="H46" t="n">
-        <v>6.998021125793457</v>
+        <v>8.415581703186035</v>
       </c>
       <c r="I46" t="n">
-        <v>7.177664279937744</v>
+        <v>8.132797956466675</v>
       </c>
       <c r="J46" t="n">
-        <v>7.946046590805054</v>
+        <v>9.145738363265991</v>
       </c>
       <c r="K46" t="n">
-        <v>8.406366348266602</v>
+        <v>9.067943334579468</v>
       </c>
       <c r="L46" t="n">
-        <v>7.481805062294006</v>
+        <v>8.075291967391967</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.690123081207275</v>
+        <v>8.045558214187622</v>
       </c>
       <c r="C47" t="n">
-        <v>8.039882183074951</v>
+        <v>7.131396055221558</v>
       </c>
       <c r="D47" t="n">
-        <v>8.590113401412964</v>
+        <v>8.400609970092773</v>
       </c>
       <c r="E47" t="n">
-        <v>8.893190383911133</v>
+        <v>9.546242475509644</v>
       </c>
       <c r="F47" t="n">
-        <v>7.295845031738281</v>
+        <v>8.24401068687439</v>
       </c>
       <c r="G47" t="n">
-        <v>8.589569091796875</v>
+        <v>7.587699890136719</v>
       </c>
       <c r="H47" t="n">
-        <v>9.622982501983643</v>
+        <v>7.669107437133789</v>
       </c>
       <c r="I47" t="n">
-        <v>8.291856527328491</v>
+        <v>7.893021821975708</v>
       </c>
       <c r="J47" t="n">
-        <v>8.960070133209229</v>
+        <v>8.890884160995483</v>
       </c>
       <c r="K47" t="n">
-        <v>7.036543607711792</v>
+        <v>8.232038021087646</v>
       </c>
       <c r="L47" t="n">
-        <v>8.401017594337464</v>
+        <v>8.164056873321533</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.385584115982056</v>
+        <v>7.563759326934814</v>
       </c>
       <c r="C48" t="n">
-        <v>6.446783065795898</v>
+        <v>6.19674825668335</v>
       </c>
       <c r="D48" t="n">
-        <v>6.971112728118896</v>
+        <v>8.585827589035034</v>
       </c>
       <c r="E48" t="n">
-        <v>7.187917232513428</v>
+        <v>8.629079818725586</v>
       </c>
       <c r="F48" t="n">
-        <v>7.982014894485474</v>
+        <v>9.514312028884888</v>
       </c>
       <c r="G48" t="n">
-        <v>8.357977390289307</v>
+        <v>5.894540786743164</v>
       </c>
       <c r="H48" t="n">
-        <v>6.259991884231567</v>
+        <v>6.1628258228302</v>
       </c>
       <c r="I48" t="n">
-        <v>6.519509553909302</v>
+        <v>8.385663747787476</v>
       </c>
       <c r="J48" t="n">
-        <v>6.781918287277222</v>
+        <v>8.185920715332031</v>
       </c>
       <c r="K48" t="n">
-        <v>7.353008031845093</v>
+        <v>6.276716709136963</v>
       </c>
       <c r="L48" t="n">
-        <v>7.024581718444824</v>
+        <v>7.539539480209351</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.587056398391724</v>
+        <v>7.513967990875244</v>
       </c>
       <c r="C49" t="n">
-        <v>7.176282167434692</v>
+        <v>7.620182991027832</v>
       </c>
       <c r="D49" t="n">
-        <v>7.894608974456787</v>
+        <v>7.669069528579712</v>
       </c>
       <c r="E49" t="n">
-        <v>7.553311347961426</v>
+        <v>7.364867925643921</v>
       </c>
       <c r="F49" t="n">
-        <v>9.302313327789307</v>
+        <v>7.024741649627686</v>
       </c>
       <c r="G49" t="n">
-        <v>7.669389247894287</v>
+        <v>7.61028790473938</v>
       </c>
       <c r="H49" t="n">
-        <v>7.113842248916626</v>
+        <v>9.463398694992065</v>
       </c>
       <c r="I49" t="n">
-        <v>10.02131009101868</v>
+        <v>7.454606771469116</v>
       </c>
       <c r="J49" t="n">
-        <v>7.343382120132446</v>
+        <v>8.009199619293213</v>
       </c>
       <c r="K49" t="n">
-        <v>8.760723114013672</v>
+        <v>8.051598310470581</v>
       </c>
       <c r="L49" t="n">
-        <v>8.042221903800964</v>
+        <v>7.778192138671875</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>6.436851739883423</v>
+        <v>8.483953714370728</v>
       </c>
       <c r="C50" t="n">
-        <v>7.456513404846191</v>
+        <v>8.48347544670105</v>
       </c>
       <c r="D50" t="n">
-        <v>9.841650724411011</v>
+        <v>7.30852746963501</v>
       </c>
       <c r="E50" t="n">
-        <v>9.056735754013062</v>
+        <v>7.659138917922974</v>
       </c>
       <c r="F50" t="n">
-        <v>8.759158611297607</v>
+        <v>7.105020999908447</v>
       </c>
       <c r="G50" t="n">
-        <v>6.957492351531982</v>
+        <v>10.89117455482483</v>
       </c>
       <c r="H50" t="n">
-        <v>6.749096870422363</v>
+        <v>9.700335025787354</v>
       </c>
       <c r="I50" t="n">
-        <v>7.281871795654297</v>
+        <v>6.70209002494812</v>
       </c>
       <c r="J50" t="n">
-        <v>6.734477996826172</v>
+        <v>8.38072657585144</v>
       </c>
       <c r="K50" t="n">
-        <v>8.950591802597046</v>
+        <v>9.044466733932495</v>
       </c>
       <c r="L50" t="n">
-        <v>7.822444105148316</v>
+        <v>8.375890946388244</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.134856700897217</v>
+        <v>7.460608720779419</v>
       </c>
       <c r="C51" t="n">
-        <v>8.299955368041992</v>
+        <v>6.968904495239258</v>
       </c>
       <c r="D51" t="n">
-        <v>8.007444858551025</v>
+        <v>8.397672176361084</v>
       </c>
       <c r="E51" t="n">
-        <v>7.41826605796814</v>
+        <v>6.966883897781372</v>
       </c>
       <c r="F51" t="n">
-        <v>7.914196729660034</v>
+        <v>7.685549736022949</v>
       </c>
       <c r="G51" t="n">
-        <v>7.783243179321289</v>
+        <v>7.31495189666748</v>
       </c>
       <c r="H51" t="n">
-        <v>9.571207046508789</v>
+        <v>8.63114857673645</v>
       </c>
       <c r="I51" t="n">
-        <v>9.13463282585144</v>
+        <v>7.480923652648926</v>
       </c>
       <c r="J51" t="n">
-        <v>8.291208028793335</v>
+        <v>8.935745477676392</v>
       </c>
       <c r="K51" t="n">
-        <v>8.326452016830444</v>
+        <v>6.850080013275146</v>
       </c>
       <c r="L51" t="n">
-        <v>8.188146281242371</v>
+        <v>7.669246864318848</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.708181691169739</v>
+        <v>7.638682532310486</v>
       </c>
       <c r="C52" t="n">
-        <v>7.618466634750366</v>
+        <v>7.491709861755371</v>
       </c>
       <c r="D52" t="n">
-        <v>7.632026414871216</v>
+        <v>7.4110400390625</v>
       </c>
       <c r="E52" t="n">
-        <v>7.512530317306519</v>
+        <v>7.616621537208557</v>
       </c>
       <c r="F52" t="n">
-        <v>7.691087131500244</v>
+        <v>7.596165542602539</v>
       </c>
       <c r="G52" t="n">
-        <v>7.775015683174133</v>
+        <v>7.521305799484253</v>
       </c>
       <c r="H52" t="n">
-        <v>7.848419313430786</v>
+        <v>7.67411678314209</v>
       </c>
       <c r="I52" t="n">
-        <v>7.620841312408447</v>
+        <v>7.682942848205567</v>
       </c>
       <c r="J52" t="n">
-        <v>7.750900745391846</v>
+        <v>7.679736413955689</v>
       </c>
       <c r="K52" t="n">
-        <v>7.81985894203186</v>
+        <v>7.730848813056946</v>
       </c>
       <c r="L52" t="n">
-        <v>7.697732818603515</v>
+        <v>7.6043170170784</v>
       </c>
     </row>
   </sheetData>
